--- a/docs/mat-bang-neo-9-be/bang_thong_ke_neo_9_be.xlsx
+++ b/docs/mat-bang-neo-9-be/bang_thong_ke_neo_9_be.xlsx
@@ -2523,7 +2523,7 @@
         <v>6.5</v>
       </c>
       <c r="K38">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="L38">
         <v>44.6</v>
@@ -2585,7 +2585,7 @@
         <v>6.5</v>
       </c>
       <c r="K39">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="L39">
         <v>44.6</v>
@@ -2647,7 +2647,7 @@
         <v>6.5</v>
       </c>
       <c r="K40">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="L40">
         <v>44.6</v>
@@ -2709,7 +2709,7 @@
         <v>6.5</v>
       </c>
       <c r="K41">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="L41">
         <v>44.6</v>
@@ -2771,7 +2771,7 @@
         <v>6.5</v>
       </c>
       <c r="K42">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="L42">
         <v>44.6</v>
@@ -2833,7 +2833,7 @@
         <v>6.5</v>
       </c>
       <c r="K43">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="L43">
         <v>44.6</v>
@@ -2895,7 +2895,7 @@
         <v>6.5</v>
       </c>
       <c r="K44">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="L44">
         <v>44.6</v>
@@ -2957,7 +2957,7 @@
         <v>6.5</v>
       </c>
       <c r="K45">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="L45">
         <v>44.6</v>
@@ -3019,7 +3019,7 @@
         <v>6.5</v>
       </c>
       <c r="K46">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="L46">
         <v>44.6</v>
@@ -3081,7 +3081,7 @@
         <v>6.5</v>
       </c>
       <c r="K47">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="L47">
         <v>44.6</v>
@@ -3143,7 +3143,7 @@
         <v>6.5</v>
       </c>
       <c r="K48">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="L48">
         <v>44.6</v>
@@ -3205,7 +3205,7 @@
         <v>6.5</v>
       </c>
       <c r="K49">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="L49">
         <v>44.6</v>
@@ -3267,7 +3267,7 @@
         <v>6.5</v>
       </c>
       <c r="K50">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="L50">
         <v>44.6</v>
@@ -3329,7 +3329,7 @@
         <v>6.5</v>
       </c>
       <c r="K51">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="L51">
         <v>44.6</v>
@@ -3391,7 +3391,7 @@
         <v>6.5</v>
       </c>
       <c r="K52">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="L52">
         <v>44.6</v>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>HV-P061</v>
+        <v>HV-P062</v>
       </c>
       <c r="B53" t="str">
         <v>B3A-D01</v>
@@ -3485,7 +3485,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>HV-P062</v>
+        <v>HV-P063</v>
       </c>
       <c r="B54" t="str">
         <v>B3A-D02</v>
@@ -3547,7 +3547,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>HV-P063</v>
+        <v>HV-P064</v>
       </c>
       <c r="B55" t="str">
         <v>B3A-D03</v>
@@ -3609,7 +3609,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>HV-P064</v>
+        <v>HV-P065</v>
       </c>
       <c r="B56" t="str">
         <v>B3A-D04</v>
@@ -3671,7 +3671,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>HV-P065</v>
+        <v>HV-P066</v>
       </c>
       <c r="B57" t="str">
         <v>B3A-D05</v>
@@ -3733,7 +3733,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>HV-P066</v>
+        <v>HV-P067</v>
       </c>
       <c r="B58" t="str">
         <v>B3A-D06</v>
@@ -3795,7 +3795,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>HV-P067</v>
+        <v>HV-P068</v>
       </c>
       <c r="B59" t="str">
         <v>B3A-D07</v>
@@ -3857,7 +3857,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>HV-P068</v>
+        <v>HV-P069</v>
       </c>
       <c r="B60" t="str">
         <v>B3A-D08</v>
@@ -3919,7 +3919,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>HV-P069</v>
+        <v>HV-P070</v>
       </c>
       <c r="B61" t="str">
         <v>B3A-D09</v>
@@ -3981,7 +3981,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>HV-P070</v>
+        <v>HV-P071</v>
       </c>
       <c r="B62" t="str">
         <v>B3A-D10</v>
@@ -4043,7 +4043,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>HV-P071</v>
+        <v>HV-P072</v>
       </c>
       <c r="B63" t="str">
         <v>B3A-D11</v>
@@ -4105,7 +4105,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>HV-P072</v>
+        <v>HV-P073</v>
       </c>
       <c r="B64" t="str">
         <v>B3A-D12</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>HV-P073</v>
+        <v>HV-P074</v>
       </c>
       <c r="B65" t="str">
         <v>B3A-D13</v>
@@ -4229,7 +4229,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>HV-P074</v>
+        <v>HV-P075</v>
       </c>
       <c r="B66" t="str">
         <v>B3A-D14</v>
@@ -4291,7 +4291,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>HV-P075</v>
+        <v>HV-P076</v>
       </c>
       <c r="B67" t="str">
         <v>B3A-D15</v>
@@ -4353,7 +4353,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>HV-P076</v>
+        <v>HV-P077</v>
       </c>
       <c r="B68" t="str">
         <v>B3A-D16</v>
@@ -4415,7 +4415,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>HV-P077</v>
+        <v>HV-P078</v>
       </c>
       <c r="B69" t="str">
         <v>B3A-D17</v>
@@ -4477,7 +4477,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>HV-P078</v>
+        <v>HV-P079</v>
       </c>
       <c r="B70" t="str">
         <v>B3A-D18</v>
@@ -4539,7 +4539,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>HV-P079</v>
+        <v>HV-P080</v>
       </c>
       <c r="B71" t="str">
         <v>B3A-D19</v>
@@ -4601,7 +4601,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>HV-P080</v>
+        <v>HV-P081</v>
       </c>
       <c r="B72" t="str">
         <v>B3A-D20</v>
@@ -4663,7 +4663,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>HV-P085</v>
+        <v>HV-P086</v>
       </c>
       <c r="B73" t="str">
         <v>B3A-D25</v>
@@ -4725,7 +4725,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>HV-P086</v>
+        <v>HV-P087</v>
       </c>
       <c r="B74" t="str">
         <v>B3A-D26</v>
@@ -4787,7 +4787,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>HV-P087</v>
+        <v>HV-P088</v>
       </c>
       <c r="B75" t="str">
         <v>B3A-D27</v>
@@ -4849,7 +4849,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>HV-P088</v>
+        <v>HV-P089</v>
       </c>
       <c r="B76" t="str">
         <v>B3A-D28</v>
@@ -4911,7 +4911,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>HV-P089</v>
+        <v>HV-P090</v>
       </c>
       <c r="B77" t="str">
         <v>B3A-D29</v>
@@ -4973,7 +4973,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>HV-P090</v>
+        <v>HV-P091</v>
       </c>
       <c r="B78" t="str">
         <v>B3A-D30</v>
@@ -5035,7 +5035,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>HV-P091</v>
+        <v>HV-P092</v>
       </c>
       <c r="B79" t="str">
         <v>B3A-D31</v>
@@ -5097,7 +5097,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>HV-P092</v>
+        <v>HV-P093</v>
       </c>
       <c r="B80" t="str">
         <v>B3A-D32</v>
@@ -5159,7 +5159,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>HV-P093</v>
+        <v>HV-P094</v>
       </c>
       <c r="B81" t="str">
         <v>B3A-D33</v>
@@ -5221,7 +5221,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>HV-P094</v>
+        <v>HV-P095</v>
       </c>
       <c r="B82" t="str">
         <v>B3A-D34</v>
@@ -5283,7 +5283,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>HV-P095</v>
+        <v>HV-P096</v>
       </c>
       <c r="B83" t="str">
         <v>B3A-D35</v>
@@ -5345,7 +5345,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>HV-P111</v>
+        <v>HV-P112</v>
       </c>
       <c r="B84" t="str">
         <v>B5A-D01</v>
@@ -5407,7 +5407,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>HV-P112</v>
+        <v>HV-P113</v>
       </c>
       <c r="B85" t="str">
         <v>B5A-D02</v>
@@ -5469,7 +5469,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>HV-P113</v>
+        <v>HV-P114</v>
       </c>
       <c r="B86" t="str">
         <v>B5A-D03</v>
@@ -5531,7 +5531,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>HV-P114</v>
+        <v>HV-P115</v>
       </c>
       <c r="B87" t="str">
         <v>B5A-D04</v>
@@ -5593,7 +5593,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>HV-P115</v>
+        <v>HV-P116</v>
       </c>
       <c r="B88" t="str">
         <v>B5A-D05</v>
@@ -5655,7 +5655,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>HV-P116</v>
+        <v>HV-P117</v>
       </c>
       <c r="B89" t="str">
         <v>B5A-D06</v>
@@ -5717,7 +5717,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>HV-P117</v>
+        <v>HV-P118</v>
       </c>
       <c r="B90" t="str">
         <v>B5A-D07</v>
@@ -5779,7 +5779,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>HV-P118</v>
+        <v>HV-P119</v>
       </c>
       <c r="B91" t="str">
         <v>B5A-D08</v>
@@ -5841,7 +5841,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>HV-P119</v>
+        <v>HV-P120</v>
       </c>
       <c r="B92" t="str">
         <v>B5A-D09</v>
@@ -5903,7 +5903,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>HV-P120</v>
+        <v>HV-P121</v>
       </c>
       <c r="B93" t="str">
         <v>B5A-D10</v>
@@ -5965,7 +5965,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>HV-P121</v>
+        <v>HV-P122</v>
       </c>
       <c r="B94" t="str">
         <v>B5A-D11</v>
@@ -6027,7 +6027,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>HV-P122</v>
+        <v>HV-P123</v>
       </c>
       <c r="B95" t="str">
         <v>B5A-D12</v>
@@ -6089,7 +6089,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>HV-P126</v>
+        <v>HV-P127</v>
       </c>
       <c r="B96" t="str">
         <v>B5A-D16</v>
@@ -6151,7 +6151,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>HV-P127</v>
+        <v>HV-P128</v>
       </c>
       <c r="B97" t="str">
         <v>B5A-D17</v>
@@ -6213,7 +6213,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>HV-P128</v>
+        <v>HV-P129</v>
       </c>
       <c r="B98" t="str">
         <v>B5A-D18</v>
@@ -6275,7 +6275,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>HV-P129</v>
+        <v>HV-P130</v>
       </c>
       <c r="B99" t="str">
         <v>B5A-D19</v>
@@ -6337,7 +6337,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>HV-P130</v>
+        <v>HV-P131</v>
       </c>
       <c r="B100" t="str">
         <v>B5A-D20</v>
@@ -6399,7 +6399,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>HV-P131</v>
+        <v>HV-P132</v>
       </c>
       <c r="B101" t="str">
         <v>B5A-D21</v>
@@ -6461,7 +6461,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>HV-P132</v>
+        <v>HV-P133</v>
       </c>
       <c r="B102" t="str">
         <v>B5A-D22</v>
@@ -6523,7 +6523,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>HV-P143</v>
+        <v>HV-P144</v>
       </c>
       <c r="B103" t="str">
         <v>B5A-D33</v>
@@ -6585,7 +6585,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>HV-P144</v>
+        <v>HV-P145</v>
       </c>
       <c r="B104" t="str">
         <v>B5A-D34</v>
@@ -6647,7 +6647,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>HV-P145</v>
+        <v>HV-P146</v>
       </c>
       <c r="B105" t="str">
         <v>B5A-D35</v>
@@ -6709,7 +6709,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>HV-P146</v>
+        <v>HV-P147</v>
       </c>
       <c r="B106" t="str">
         <v>B5A-D36</v>
@@ -6771,7 +6771,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>HV-P147</v>
+        <v>HV-P148</v>
       </c>
       <c r="B107" t="str">
         <v>B5A-D37</v>
@@ -6833,7 +6833,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>HV-P148</v>
+        <v>HV-P149</v>
       </c>
       <c r="B108" t="str">
         <v>B5A-D38</v>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>HV-P149</v>
+        <v>HV-P150</v>
       </c>
       <c r="B109" t="str">
         <v>B5A-D39</v>
@@ -6957,7 +6957,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>HV-P150</v>
+        <v>HV-P151</v>
       </c>
       <c r="B110" t="str">
         <v>B5A-D40</v>
@@ -7019,7 +7019,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>HV-P151</v>
+        <v>HV-P152</v>
       </c>
       <c r="B111" t="str">
         <v>B5A-D41</v>
@@ -7081,7 +7081,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>HV-P152</v>
+        <v>HV-P153</v>
       </c>
       <c r="B112" t="str">
         <v>B5A-D42</v>
@@ -7143,7 +7143,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>HV-P153</v>
+        <v>HV-P154</v>
       </c>
       <c r="B113" t="str">
         <v>B5A-D43</v>
@@ -7205,7 +7205,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>HV-P154</v>
+        <v>HV-P155</v>
       </c>
       <c r="B114" t="str">
         <v>B5A-D44</v>
@@ -7267,7 +7267,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>HV-P155</v>
+        <v>HV-P156</v>
       </c>
       <c r="B115" t="str">
         <v>B5A-D45</v>
@@ -7329,7 +7329,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>HV-P156</v>
+        <v>HV-P157</v>
       </c>
       <c r="B116" t="str">
         <v>B5A-D46</v>
@@ -7391,7 +7391,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>HV-P157</v>
+        <v>HV-P158</v>
       </c>
       <c r="B117" t="str">
         <v>B5A-D47</v>
@@ -7453,7 +7453,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>HV-P158</v>
+        <v>HV-P159</v>
       </c>
       <c r="B118" t="str">
         <v>B5A-D48</v>
@@ -7515,7 +7515,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>HV-P159</v>
+        <v>HV-P160</v>
       </c>
       <c r="B119" t="str">
         <v>B5A-D49</v>
@@ -7577,7 +7577,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>HV-P160</v>
+        <v>HV-P161</v>
       </c>
       <c r="B120" t="str">
         <v>B6-D01</v>
@@ -7607,7 +7607,7 @@
         <v>6.5</v>
       </c>
       <c r="K120">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L120">
         <v>44.6</v>
@@ -7639,7 +7639,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>HV-P161</v>
+        <v>HV-P162</v>
       </c>
       <c r="B121" t="str">
         <v>B6-D02</v>
@@ -7669,7 +7669,7 @@
         <v>6.5</v>
       </c>
       <c r="K121">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L121">
         <v>44.6</v>
@@ -7701,7 +7701,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>HV-P162</v>
+        <v>HV-P163</v>
       </c>
       <c r="B122" t="str">
         <v>B6-D03</v>
@@ -7731,7 +7731,7 @@
         <v>6.5</v>
       </c>
       <c r="K122">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L122">
         <v>44.6</v>
@@ -7763,7 +7763,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>HV-P163</v>
+        <v>HV-P164</v>
       </c>
       <c r="B123" t="str">
         <v>B6-D04</v>
@@ -7793,7 +7793,7 @@
         <v>6.5</v>
       </c>
       <c r="K123">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L123">
         <v>44.6</v>
@@ -7825,7 +7825,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>HV-P164</v>
+        <v>HV-P165</v>
       </c>
       <c r="B124" t="str">
         <v>B6-D05</v>
@@ -7855,7 +7855,7 @@
         <v>6.5</v>
       </c>
       <c r="K124">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L124">
         <v>44.6</v>
@@ -7887,7 +7887,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>HV-P165</v>
+        <v>HV-P166</v>
       </c>
       <c r="B125" t="str">
         <v>B6-D06</v>
@@ -7917,7 +7917,7 @@
         <v>6.5</v>
       </c>
       <c r="K125">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L125">
         <v>44.6</v>
@@ -7949,7 +7949,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>HV-P166</v>
+        <v>HV-P167</v>
       </c>
       <c r="B126" t="str">
         <v>B6-D07</v>
@@ -7979,7 +7979,7 @@
         <v>6.5</v>
       </c>
       <c r="K126">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L126">
         <v>44.6</v>
@@ -8011,7 +8011,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>HV-P167</v>
+        <v>HV-P168</v>
       </c>
       <c r="B127" t="str">
         <v>B6-D08</v>
@@ -8041,7 +8041,7 @@
         <v>6.5</v>
       </c>
       <c r="K127">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L127">
         <v>44.6</v>
@@ -8073,7 +8073,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>HV-P168</v>
+        <v>HV-P169</v>
       </c>
       <c r="B128" t="str">
         <v>B6-D09</v>
@@ -8103,7 +8103,7 @@
         <v>6.5</v>
       </c>
       <c r="K128">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L128">
         <v>44.6</v>
@@ -8135,7 +8135,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>HV-P169</v>
+        <v>HV-P170</v>
       </c>
       <c r="B129" t="str">
         <v>B6-D10</v>
@@ -8165,7 +8165,7 @@
         <v>6.5</v>
       </c>
       <c r="K129">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L129">
         <v>44.6</v>
@@ -8197,7 +8197,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>HV-P170</v>
+        <v>HV-P171</v>
       </c>
       <c r="B130" t="str">
         <v>B6-D11</v>
@@ -8227,7 +8227,7 @@
         <v>6.5</v>
       </c>
       <c r="K130">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L130">
         <v>44.6</v>
@@ -8259,7 +8259,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>HV-P171</v>
+        <v>HV-P172</v>
       </c>
       <c r="B131" t="str">
         <v>B6-D12</v>
@@ -8289,7 +8289,7 @@
         <v>6.5</v>
       </c>
       <c r="K131">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L131">
         <v>44.6</v>
@@ -8321,7 +8321,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>HV-P172</v>
+        <v>HV-P173</v>
       </c>
       <c r="B132" t="str">
         <v>B6-D13</v>
@@ -8351,7 +8351,7 @@
         <v>6.5</v>
       </c>
       <c r="K132">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L132">
         <v>44.6</v>
@@ -8383,7 +8383,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>HV-P173</v>
+        <v>HV-P174</v>
       </c>
       <c r="B133" t="str">
         <v>B6-D14</v>
@@ -8413,7 +8413,7 @@
         <v>6.5</v>
       </c>
       <c r="K133">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L133">
         <v>44.6</v>
@@ -8445,7 +8445,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>HV-P174</v>
+        <v>HV-P175</v>
       </c>
       <c r="B134" t="str">
         <v>B6-D15</v>
@@ -8475,7 +8475,7 @@
         <v>6.5</v>
       </c>
       <c r="K134">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L134">
         <v>44.6</v>
@@ -8507,7 +8507,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>HV-P175</v>
+        <v>HV-P176</v>
       </c>
       <c r="B135" t="str">
         <v>B6-D16</v>
@@ -8537,7 +8537,7 @@
         <v>6.5</v>
       </c>
       <c r="K135">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L135">
         <v>44.6</v>
@@ -8569,7 +8569,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>HV-P177</v>
+        <v>HV-P178</v>
       </c>
       <c r="B136" t="str">
         <v>B6-D18</v>
@@ -8599,7 +8599,7 @@
         <v>6.5</v>
       </c>
       <c r="K136">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L136">
         <v>44.6</v>
@@ -8631,7 +8631,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>HV-P178</v>
+        <v>HV-P179</v>
       </c>
       <c r="B137" t="str">
         <v>B6-D19</v>
@@ -8661,7 +8661,7 @@
         <v>6.5</v>
       </c>
       <c r="K137">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L137">
         <v>44.6</v>
@@ -8693,7 +8693,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>HV-P179</v>
+        <v>HV-P180</v>
       </c>
       <c r="B138" t="str">
         <v>B6-D20</v>
@@ -8723,7 +8723,7 @@
         <v>6.5</v>
       </c>
       <c r="K138">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L138">
         <v>44.6</v>
@@ -8755,7 +8755,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>HV-P180</v>
+        <v>HV-P181</v>
       </c>
       <c r="B139" t="str">
         <v>B6-D21</v>
@@ -8785,7 +8785,7 @@
         <v>6.5</v>
       </c>
       <c r="K139">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L139">
         <v>44.6</v>
@@ -8817,7 +8817,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>HV-P181</v>
+        <v>HV-P182</v>
       </c>
       <c r="B140" t="str">
         <v>B6-D22</v>
@@ -8847,7 +8847,7 @@
         <v>6.5</v>
       </c>
       <c r="K140">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L140">
         <v>44.6</v>
@@ -8879,7 +8879,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>HV-P182</v>
+        <v>HV-P183</v>
       </c>
       <c r="B141" t="str">
         <v>B6-D23</v>
@@ -8909,7 +8909,7 @@
         <v>6.5</v>
       </c>
       <c r="K141">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L141">
         <v>44.6</v>
@@ -8941,7 +8941,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>HV-P183</v>
+        <v>HV-P184</v>
       </c>
       <c r="B142" t="str">
         <v>B6-D24</v>
@@ -8971,7 +8971,7 @@
         <v>6.5</v>
       </c>
       <c r="K142">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L142">
         <v>44.6</v>
@@ -9003,7 +9003,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>HV-P184</v>
+        <v>HV-P185</v>
       </c>
       <c r="B143" t="str">
         <v>B6-D25</v>
@@ -9033,7 +9033,7 @@
         <v>6.5</v>
       </c>
       <c r="K143">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L143">
         <v>44.6</v>
@@ -9065,7 +9065,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>HV-P185</v>
+        <v>HV-P186</v>
       </c>
       <c r="B144" t="str">
         <v>B6-D26</v>
@@ -9095,7 +9095,7 @@
         <v>6.5</v>
       </c>
       <c r="K144">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L144">
         <v>44.6</v>
@@ -9127,7 +9127,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>HV-P187</v>
+        <v>HV-P188</v>
       </c>
       <c r="B145" t="str">
         <v>B6-D28</v>
@@ -9157,7 +9157,7 @@
         <v>6.5</v>
       </c>
       <c r="K145">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L145">
         <v>44.6</v>
@@ -9189,7 +9189,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>HV-P188</v>
+        <v>HV-P189</v>
       </c>
       <c r="B146" t="str">
         <v>B6-D29</v>
@@ -9219,7 +9219,7 @@
         <v>6.5</v>
       </c>
       <c r="K146">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L146">
         <v>44.6</v>
@@ -9251,7 +9251,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>HV-P189</v>
+        <v>HV-P190</v>
       </c>
       <c r="B147" t="str">
         <v>B6-D30</v>
@@ -9281,7 +9281,7 @@
         <v>6.5</v>
       </c>
       <c r="K147">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="L147">
         <v>44.6</v>
@@ -9313,7 +9313,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>HV-P190</v>
+        <v>HV-P192</v>
       </c>
       <c r="B148" t="str">
         <v>B7-D01</v>
@@ -9375,7 +9375,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>HV-P191</v>
+        <v>HV-P193</v>
       </c>
       <c r="B149" t="str">
         <v>B7-D02</v>
@@ -9437,7 +9437,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>HV-P192</v>
+        <v>HV-P194</v>
       </c>
       <c r="B150" t="str">
         <v>B7-D03</v>
@@ -9499,7 +9499,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>HV-P193</v>
+        <v>HV-P195</v>
       </c>
       <c r="B151" t="str">
         <v>B7-D04</v>
@@ -9561,7 +9561,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>HV-P194</v>
+        <v>HV-P196</v>
       </c>
       <c r="B152" t="str">
         <v>B7-D05</v>
@@ -9623,7 +9623,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>HV-P195</v>
+        <v>HV-P197</v>
       </c>
       <c r="B153" t="str">
         <v>B7-D06</v>
@@ -9685,7 +9685,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>HV-P196</v>
+        <v>HV-P198</v>
       </c>
       <c r="B154" t="str">
         <v>B7-D07</v>
@@ -9747,7 +9747,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>HV-P197</v>
+        <v>HV-P199</v>
       </c>
       <c r="B155" t="str">
         <v>B7-D08</v>
@@ -9809,7 +9809,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>HV-P198</v>
+        <v>HV-P200</v>
       </c>
       <c r="B156" t="str">
         <v>B7-D09</v>
@@ -9871,7 +9871,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>HV-P199</v>
+        <v>HV-P201</v>
       </c>
       <c r="B157" t="str">
         <v>B7-D10</v>
@@ -9933,7 +9933,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>HV-P200</v>
+        <v>HV-P202</v>
       </c>
       <c r="B158" t="str">
         <v>B7-D11</v>
@@ -9995,7 +9995,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>HV-P201</v>
+        <v>HV-P203</v>
       </c>
       <c r="B159" t="str">
         <v>B7-D12</v>
@@ -10057,7 +10057,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>HV-P202</v>
+        <v>HV-P204</v>
       </c>
       <c r="B160" t="str">
         <v>B7-D13</v>
@@ -10119,7 +10119,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>HV-P203</v>
+        <v>HV-P205</v>
       </c>
       <c r="B161" t="str">
         <v>B7-D14</v>
@@ -10181,7 +10181,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>HV-P204</v>
+        <v>HV-P206</v>
       </c>
       <c r="B162" t="str">
         <v>B7-D15</v>
@@ -10243,7 +10243,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>HV-P205</v>
+        <v>HV-P207</v>
       </c>
       <c r="B163" t="str">
         <v>B7-D16</v>
@@ -10305,7 +10305,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>HV-P206</v>
+        <v>HV-P208</v>
       </c>
       <c r="B164" t="str">
         <v>B7-D17</v>
@@ -10367,7 +10367,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>HV-P207</v>
+        <v>HV-P209</v>
       </c>
       <c r="B165" t="str">
         <v>B7-D18</v>
@@ -10429,7 +10429,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>HV-P210</v>
+        <v>HV-P212</v>
       </c>
       <c r="B166" t="str">
         <v>B7-D21</v>
@@ -10491,7 +10491,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>HV-P215</v>
+        <v>HV-P217</v>
       </c>
       <c r="B167" t="str">
         <v>B7-D26</v>
@@ -10553,7 +10553,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>HV-P216</v>
+        <v>HV-P218</v>
       </c>
       <c r="B168" t="str">
         <v>B7-D27</v>
@@ -10615,7 +10615,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>HV-P217</v>
+        <v>HV-P219</v>
       </c>
       <c r="B169" t="str">
         <v>B7-D28</v>
@@ -10677,7 +10677,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>HV-P218</v>
+        <v>HV-P220</v>
       </c>
       <c r="B170" t="str">
         <v>B7-D29</v>
@@ -10739,7 +10739,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>HV-P219</v>
+        <v>HV-P221</v>
       </c>
       <c r="B171" t="str">
         <v>B7-D30</v>
@@ -10801,7 +10801,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>HV-P222</v>
+        <v>HV-P225</v>
       </c>
       <c r="B172" t="str">
         <v>B8-D01</v>
@@ -10863,7 +10863,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>HV-P223</v>
+        <v>HV-P226</v>
       </c>
       <c r="B173" t="str">
         <v>B8-D02</v>
@@ -10925,7 +10925,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>HV-P224</v>
+        <v>HV-P227</v>
       </c>
       <c r="B174" t="str">
         <v>B8-D03</v>
@@ -10987,7 +10987,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>HV-P225</v>
+        <v>HV-P228</v>
       </c>
       <c r="B175" t="str">
         <v>B8-D04</v>
@@ -11049,7 +11049,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>HV-P226</v>
+        <v>HV-P229</v>
       </c>
       <c r="B176" t="str">
         <v>B8-D05</v>
@@ -11111,7 +11111,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>HV-P227</v>
+        <v>HV-P230</v>
       </c>
       <c r="B177" t="str">
         <v>B8-D06</v>
@@ -11173,7 +11173,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>HV-P228</v>
+        <v>HV-P231</v>
       </c>
       <c r="B178" t="str">
         <v>B8-D07</v>
@@ -11235,7 +11235,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>HV-P229</v>
+        <v>HV-P232</v>
       </c>
       <c r="B179" t="str">
         <v>B8-D08</v>
@@ -11297,7 +11297,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>HV-P230</v>
+        <v>HV-P233</v>
       </c>
       <c r="B180" t="str">
         <v>B8-D09</v>
@@ -11359,7 +11359,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>HV-P231</v>
+        <v>HV-P234</v>
       </c>
       <c r="B181" t="str">
         <v>B8-D10</v>
@@ -11421,7 +11421,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>HV-P232</v>
+        <v>HV-P235</v>
       </c>
       <c r="B182" t="str">
         <v>B8-D11</v>
@@ -11483,7 +11483,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>HV-P233</v>
+        <v>HV-P236</v>
       </c>
       <c r="B183" t="str">
         <v>B8-D12</v>
@@ -11545,7 +11545,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>HV-P234</v>
+        <v>HV-P237</v>
       </c>
       <c r="B184" t="str">
         <v>B8-D13</v>
@@ -11607,7 +11607,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>HV-P235</v>
+        <v>HV-P238</v>
       </c>
       <c r="B185" t="str">
         <v>B8-D14</v>
@@ -11669,7 +11669,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>HV-P236</v>
+        <v>HV-P239</v>
       </c>
       <c r="B186" t="str">
         <v>B8-D15</v>
@@ -11731,7 +11731,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>HV-P237</v>
+        <v>HV-P240</v>
       </c>
       <c r="B187" t="str">
         <v>B8-D16</v>
@@ -11793,7 +11793,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>HV-P238</v>
+        <v>HV-P241</v>
       </c>
       <c r="B188" t="str">
         <v>B8-D17</v>
@@ -11855,7 +11855,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>HV-P239</v>
+        <v>HV-P242</v>
       </c>
       <c r="B189" t="str">
         <v>B8-D18</v>
@@ -11917,7 +11917,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>HV-P240</v>
+        <v>HV-P243</v>
       </c>
       <c r="B190" t="str">
         <v>B8-D19</v>
@@ -11979,7 +11979,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>HV-P241</v>
+        <v>HV-P244</v>
       </c>
       <c r="B191" t="str">
         <v>B8-D20</v>
@@ -12041,7 +12041,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>HV-P242</v>
+        <v>HV-P245</v>
       </c>
       <c r="B192" t="str">
         <v>B8-D21</v>
@@ -12103,7 +12103,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>HV-P243</v>
+        <v>HV-P246</v>
       </c>
       <c r="B193" t="str">
         <v>B8-D22</v>
@@ -12165,7 +12165,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>HV-P244</v>
+        <v>HV-P247</v>
       </c>
       <c r="B194" t="str">
         <v>B8-D23</v>
@@ -12227,7 +12227,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>HV-P245</v>
+        <v>HV-P248</v>
       </c>
       <c r="B195" t="str">
         <v>B8-D24</v>
@@ -12289,7 +12289,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>HV-P246</v>
+        <v>HV-P249</v>
       </c>
       <c r="B196" t="str">
         <v>B8-D25</v>
@@ -12351,7 +12351,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>HV-P247</v>
+        <v>HV-P250</v>
       </c>
       <c r="B197" t="str">
         <v>B8-D26</v>
@@ -12413,7 +12413,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>HV-P248</v>
+        <v>HV-P251</v>
       </c>
       <c r="B198" t="str">
         <v>B8-D27</v>
@@ -12475,7 +12475,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>HV-P249</v>
+        <v>HV-P252</v>
       </c>
       <c r="B199" t="str">
         <v>B8-D28</v>
@@ -12537,7 +12537,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>HV-P254</v>
+        <v>HV-P257</v>
       </c>
       <c r="B200" t="str">
         <v>B8-D33</v>
@@ -12599,7 +12599,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>HV-P255</v>
+        <v>HV-P258</v>
       </c>
       <c r="B201" t="str">
         <v>B8-D34</v>
@@ -12661,7 +12661,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>HV-P256</v>
+        <v>HV-P259</v>
       </c>
       <c r="B202" t="str">
         <v>B8-D35</v>
@@ -12723,7 +12723,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>HV-P257</v>
+        <v>HV-P260</v>
       </c>
       <c r="B203" t="str">
         <v>B8-D36</v>
@@ -12785,7 +12785,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>HV-P258</v>
+        <v>HV-P261</v>
       </c>
       <c r="B204" t="str">
         <v>B8-D37</v>
@@ -12847,7 +12847,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>HV-P259</v>
+        <v>HV-P262</v>
       </c>
       <c r="B205" t="str">
         <v>B8-D38</v>
@@ -12909,7 +12909,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>HV-P260</v>
+        <v>HV-P263</v>
       </c>
       <c r="B206" t="str">
         <v>B8-D39</v>
@@ -12971,7 +12971,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>HV-P261</v>
+        <v>HV-P264</v>
       </c>
       <c r="B207" t="str">
         <v>B8-D40</v>
@@ -13033,7 +13033,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>HV-P262</v>
+        <v>HV-P265</v>
       </c>
       <c r="B208" t="str">
         <v>B8-D41</v>
@@ -13095,7 +13095,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>HV-P263</v>
+        <v>HV-P266</v>
       </c>
       <c r="B209" t="str">
         <v>B8-D42</v>
@@ -13157,7 +13157,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>HV-P264</v>
+        <v>HV-P267</v>
       </c>
       <c r="B210" t="str">
         <v>B8-D43</v>
@@ -13219,7 +13219,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>HV-P265</v>
+        <v>HV-P268</v>
       </c>
       <c r="B211" t="str">
         <v>B8-D44</v>
@@ -13281,7 +13281,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>HV-P266</v>
+        <v>HV-P269</v>
       </c>
       <c r="B212" t="str">
         <v>B8-D45</v>
@@ -13343,7 +13343,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>HV-P267</v>
+        <v>HV-P270</v>
       </c>
       <c r="B213" t="str">
         <v>B8-D46</v>
@@ -13405,7 +13405,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>HV-P268</v>
+        <v>HV-P271</v>
       </c>
       <c r="B214" t="str">
         <v>B8-D47</v>
@@ -13467,7 +13467,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>HV-P270</v>
+        <v>HV-P273</v>
       </c>
       <c r="B215" t="str">
         <v>B8-D49</v>
@@ -13529,7 +13529,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>HV-P271</v>
+        <v>HV-P274</v>
       </c>
       <c r="B216" t="str">
         <v>B8-D50</v>
@@ -13591,7 +13591,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>HV-P272</v>
+        <v>HV-P275</v>
       </c>
       <c r="B217" t="str">
         <v>B8-D51</v>
@@ -13653,7 +13653,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>HV-P273</v>
+        <v>HV-P276</v>
       </c>
       <c r="B218" t="str">
         <v>B9-D01</v>
@@ -13715,7 +13715,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>HV-P274</v>
+        <v>HV-P277</v>
       </c>
       <c r="B219" t="str">
         <v>B9-D02</v>
@@ -13777,7 +13777,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>HV-P275</v>
+        <v>HV-P278</v>
       </c>
       <c r="B220" t="str">
         <v>B9-D03</v>
@@ -13839,7 +13839,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>HV-P276</v>
+        <v>HV-P279</v>
       </c>
       <c r="B221" t="str">
         <v>B9-D04</v>
@@ -13901,7 +13901,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>HV-P277</v>
+        <v>HV-P280</v>
       </c>
       <c r="B222" t="str">
         <v>B9-D05</v>
@@ -13963,7 +13963,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>HV-P278</v>
+        <v>HV-P281</v>
       </c>
       <c r="B223" t="str">
         <v>B9-D06</v>
@@ -14025,7 +14025,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>HV-P279</v>
+        <v>HV-P282</v>
       </c>
       <c r="B224" t="str">
         <v>B9-D07</v>
@@ -14087,7 +14087,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>HV-P280</v>
+        <v>HV-P283</v>
       </c>
       <c r="B225" t="str">
         <v>B9-D08</v>
@@ -14149,7 +14149,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>HV-P281</v>
+        <v>HV-P284</v>
       </c>
       <c r="B226" t="str">
         <v>B9-D09</v>
@@ -14211,7 +14211,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>HV-P282</v>
+        <v>HV-P285</v>
       </c>
       <c r="B227" t="str">
         <v>B9-D10</v>
@@ -14273,7 +14273,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>HV-P283</v>
+        <v>HV-P286</v>
       </c>
       <c r="B228" t="str">
         <v>B9-D11</v>
@@ -14335,7 +14335,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>HV-P284</v>
+        <v>HV-P287</v>
       </c>
       <c r="B229" t="str">
         <v>B9-D12</v>
@@ -14397,7 +14397,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>HV-P285</v>
+        <v>HV-P288</v>
       </c>
       <c r="B230" t="str">
         <v>B9-D13</v>
@@ -14459,7 +14459,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>HV-P286</v>
+        <v>HV-P289</v>
       </c>
       <c r="B231" t="str">
         <v>B9-D14</v>
@@ -14521,7 +14521,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>HV-P287</v>
+        <v>HV-P290</v>
       </c>
       <c r="B232" t="str">
         <v>B9-D15</v>
@@ -14583,7 +14583,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>HV-P289</v>
+        <v>HV-P292</v>
       </c>
       <c r="B233" t="str">
         <v>B9-D17</v>
@@ -14645,7 +14645,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>HV-P290</v>
+        <v>HV-P293</v>
       </c>
       <c r="B234" t="str">
         <v>B9-D18</v>
@@ -14707,7 +14707,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>HV-P291</v>
+        <v>HV-P294</v>
       </c>
       <c r="B235" t="str">
         <v>B9-D19</v>
@@ -14769,7 +14769,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>HV-P292</v>
+        <v>HV-P295</v>
       </c>
       <c r="B236" t="str">
         <v>B9-D20</v>
@@ -14868,7 +14868,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>BẢNG THỐNG KÊ ĐẾ NEO ĐÁY HỒ: ĐẾ BTCT + VÍT XOẮN (32 ĐẾ, 29 ĐẾ DÙNG CHUNG, 61 TUYẾN CÁP) — HV-FPV-2026</v>
+        <v>BẢNG THỐNG KÊ ĐẾ NEO ĐÁY HỒ: ĐẾ BTCT + VÍT XOẮN (32 ĐẾ, 32 ĐẾ DÙNG CHUNG, 64 TUYẾN CÁP) — HV-FPV-2026</v>
       </c>
     </row>
     <row r="2">
@@ -15113,28 +15113,28 @@
         <v>HV-DV003</v>
       </c>
       <c r="B8" t="str">
-        <v>B2-D12</v>
+        <v>B2-D12 + B3-D22</v>
       </c>
       <c r="C8" t="str">
-        <v>BÈ 2</v>
+        <v>BÈ 2 + BÈ 3</v>
       </c>
       <c r="D8" t="str">
-        <v>ĐƠN</v>
+        <v>DÙNG CHUNG</v>
       </c>
       <c r="E8">
-        <v>-38.99</v>
+        <v>-42.64</v>
       </c>
       <c r="F8">
-        <v>-26.62</v>
+        <v>-28.74</v>
       </c>
       <c r="G8">
         <v>378.3</v>
       </c>
       <c r="H8">
-        <v>10.75</v>
+        <v>10.07</v>
       </c>
       <c r="I8">
-        <v>129.3</v>
+        <v>152.4</v>
       </c>
       <c r="J8">
         <v>2.5</v>
@@ -15158,19 +15158,19 @@
         <v>14.8</v>
       </c>
       <c r="Q8">
-        <v>27.8</v>
+        <v>38.6</v>
       </c>
       <c r="R8">
-        <v>0.24</v>
+        <v>0.59</v>
       </c>
       <c r="S8">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="T8">
-        <v>0.38</v>
+        <v>0.63</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="V8">
         <v>0.15</v>
@@ -15232,19 +15232,19 @@
         <v>14.8</v>
       </c>
       <c r="Q9">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="R9">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="S9">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="T9">
-        <v>0.71</v>
+        <v>0.69</v>
       </c>
       <c r="U9">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="V9">
         <v>0.15</v>
@@ -15306,19 +15306,19 @@
         <v>14.8</v>
       </c>
       <c r="Q10">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="R10">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="S10">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="T10">
-        <v>0.57</v>
+        <v>0.56</v>
       </c>
       <c r="U10">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="V10">
         <v>0.15</v>
@@ -15383,16 +15383,16 @@
         <v>73.7</v>
       </c>
       <c r="R11">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="S11">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="T11">
-        <v>0.94</v>
+        <v>0.93</v>
       </c>
       <c r="U11">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="V11">
         <v>0.15</v>
@@ -15433,19 +15433,19 @@
         <v>116.8</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="K12">
         <v>0.4</v>
       </c>
       <c r="L12">
-        <v>3.58</v>
+        <v>3.01</v>
       </c>
       <c r="M12">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="N12">
-        <v>9.2</v>
+        <v>7.7</v>
       </c>
       <c r="O12">
         <v>4</v>
@@ -15457,16 +15457,16 @@
         <v>73.7</v>
       </c>
       <c r="R12">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="S12">
-        <v>0.63</v>
+        <v>0.69</v>
       </c>
       <c r="T12">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="U12">
-        <v>0.54</v>
+        <v>0.84</v>
       </c>
       <c r="V12">
         <v>0.15</v>
@@ -15534,13 +15534,13 @@
         <v>0.69</v>
       </c>
       <c r="S13">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="T13">
         <v>0.91</v>
       </c>
       <c r="U13">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="V13">
         <v>0.15</v>
@@ -15605,16 +15605,16 @@
         <v>73.7</v>
       </c>
       <c r="R14">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="S14">
         <v>0.58</v>
       </c>
       <c r="T14">
-        <v>0.94</v>
+        <v>0.93</v>
       </c>
       <c r="U14">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="V14">
         <v>0.15</v>
@@ -16789,10 +16789,10 @@
         <v>87.3</v>
       </c>
       <c r="R30">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="S30">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="T30">
         <v>0.94</v>
@@ -16815,28 +16815,28 @@
         <v>HV-DV026</v>
       </c>
       <c r="B31" t="str">
-        <v>B5A-D14</v>
+        <v>B5A-D14 + B6-D31</v>
       </c>
       <c r="C31" t="str">
-        <v>BÈ 5A</v>
+        <v>BÈ 5A + BÈ 6</v>
       </c>
       <c r="D31" t="str">
-        <v>ĐƠN</v>
+        <v>DÙNG CHUNG</v>
       </c>
       <c r="E31">
-        <v>351.47</v>
+        <v>354.71</v>
       </c>
       <c r="F31">
-        <v>-77.42</v>
+        <v>-75.89</v>
       </c>
       <c r="G31">
         <v>378.3</v>
       </c>
       <c r="H31">
-        <v>17.49</v>
+        <v>19.28</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>9.7</v>
       </c>
       <c r="J31">
         <v>2.75</v>
@@ -16863,16 +16863,16 @@
         <v>87.3</v>
       </c>
       <c r="R31">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="S31">
-        <v>0.86</v>
+        <v>0.81</v>
       </c>
       <c r="T31">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="U31">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
       <c r="V31">
         <v>0.15</v>
@@ -16946,7 +16946,7 @@
         <v>0.87</v>
       </c>
       <c r="U32">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="V32">
         <v>0.15</v>
@@ -17185,28 +17185,28 @@
         <v>HV-DV031</v>
       </c>
       <c r="B36" t="str">
-        <v>B8-D30</v>
+        <v>B7-D33 + B8-D30</v>
       </c>
       <c r="C36" t="str">
-        <v>BÈ 8</v>
+        <v>BÈ 7 + BÈ 8</v>
       </c>
       <c r="D36" t="str">
-        <v>ĐƠN</v>
+        <v>DÙNG CHUNG</v>
       </c>
       <c r="E36">
-        <v>94.4</v>
+        <v>94.38</v>
       </c>
       <c r="F36">
-        <v>90.54</v>
+        <v>90.49</v>
       </c>
       <c r="G36">
         <v>378.3</v>
       </c>
       <c r="H36">
-        <v>11.25</v>
+        <v>11.3</v>
       </c>
       <c r="I36">
-        <v>180</v>
+        <v>0.2</v>
       </c>
       <c r="J36">
         <v>2.5</v>
@@ -17233,16 +17233,16 @@
         <v>59.1</v>
       </c>
       <c r="R36">
-        <v>0.48</v>
+        <v>0.86</v>
       </c>
       <c r="S36">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="T36">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="U36">
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
       <c r="V36">
         <v>0.15</v>
@@ -17354,7 +17354,7 @@
         <v xml:space="preserve">  trong đó đế dùng chung hai bè (hai tai neo)</v>
       </c>
       <c r="B41">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C41" t="str">
         <v>đế</v>
@@ -17365,7 +17365,7 @@
         <v>Số tuyến cáp neo vào đế</v>
       </c>
       <c r="B42">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C42" t="str">
         <v>tuyến</v>
@@ -17376,7 +17376,7 @@
         <v>Tổng bê tông đế</v>
       </c>
       <c r="B43">
-        <v>94</v>
+        <v>93.4</v>
       </c>
       <c r="C43" t="str">
         <v>m³</v>
@@ -17387,7 +17387,7 @@
         <v>Tổng thép bản đế (ước tính)</v>
       </c>
       <c r="B44">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="C44" t="str">
         <v>tấn</v>
@@ -17673,22 +17673,22 @@
         <v>35.3</v>
       </c>
       <c r="H6">
-        <v>39.9</v>
+        <v>38.4</v>
       </c>
       <c r="I6">
-        <v>23.2</v>
+        <v>22.3</v>
       </c>
       <c r="J6">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="K6">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="L6">
-        <v>0.56</v>
+        <v>0.54</v>
       </c>
       <c r="M6">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="N6">
         <v>0.15</v>
@@ -17773,28 +17773,28 @@
         <v>Ø12 a200</v>
       </c>
       <c r="F8">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="G8">
-        <v>20.9</v>
+        <v>19.1</v>
       </c>
       <c r="H8">
         <v>87.2</v>
       </c>
       <c r="I8">
-        <v>31.2</v>
+        <v>28.6</v>
       </c>
       <c r="J8">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="K8">
         <v>0.86</v>
       </c>
       <c r="L8">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="M8">
-        <v>0.77</v>
+        <v>0.69</v>
       </c>
       <c r="N8">
         <v>0.15</v>
@@ -17879,22 +17879,22 @@
         <v>Ø12 a200</v>
       </c>
       <c r="F10">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G10">
-        <v>17.8</v>
+        <v>19.1</v>
       </c>
       <c r="H10">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="I10">
-        <v>12.8</v>
+        <v>13.4</v>
       </c>
       <c r="J10">
         <v>0.2</v>
       </c>
       <c r="K10">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="L10">
         <v>0.45</v>
@@ -17935,13 +17935,13 @@
         <v>4.8</v>
       </c>
       <c r="G11">
-        <v>30.7</v>
+        <v>30.5</v>
       </c>
       <c r="H11">
         <v>58.9</v>
       </c>
       <c r="I11">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="J11">
         <v>0.46</v>
@@ -18071,7 +18071,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>TÍNH TOÁN TỪNG ĐẾ NEO ĐÁY HỒ: ĐẾ BTCT + VÍT XOẮN (32 ĐẾ, 29 ĐẾ DÙNG CHUNG, 61 TUYẾN CÁP) — HV-FPV-2026</v>
+        <v>TÍNH TOÁN TỪNG ĐẾ NEO ĐÁY HỒ: ĐẾ BTCT + VÍT XOẮN (32 ĐẾ, 32 ĐẾ DÙNG CHUNG, 64 TUYẾN CÁP) — HV-FPV-2026</v>
       </c>
     </row>
     <row r="2">
@@ -18423,7 +18423,7 @@
         <v>HV-DV003</v>
       </c>
       <c r="C9" t="str">
-        <v>ĐƠN</v>
+        <v>DÙNG CHUNG</v>
       </c>
       <c r="D9" t="str">
         <v>B2-D12</v>
@@ -18435,25 +18435,25 @@
         <v>27.8</v>
       </c>
       <c r="G9">
-        <v>10.75</v>
+        <v>10.08</v>
       </c>
       <c r="H9" t="str">
-        <v>-</v>
+        <v>B3-D22</v>
       </c>
       <c r="I9" t="str">
-        <v>-</v>
-      </c>
-      <c r="J9" t="str">
-        <v>-</v>
-      </c>
-      <c r="K9" t="str">
-        <v>-</v>
+        <v>BÈ 3</v>
+      </c>
+      <c r="J9">
+        <v>38.6</v>
+      </c>
+      <c r="K9">
+        <v>10.07</v>
       </c>
       <c r="L9">
-        <v>-38.99</v>
+        <v>-42.64</v>
       </c>
       <c r="M9">
-        <v>-26.62</v>
+        <v>-28.74</v>
       </c>
       <c r="N9">
         <v>378.3</v>
@@ -18468,13 +18468,13 @@
         <v>7.7</v>
       </c>
       <c r="R9" t="str">
-        <v>B2-D12 căng (MN cao)</v>
+        <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S9">
-        <v>23.1</v>
+        <v>8.9</v>
       </c>
       <c r="T9">
-        <v>15.4</v>
+        <v>38.4</v>
       </c>
       <c r="U9">
         <v>2.5</v>
@@ -18495,16 +18495,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA9">
-        <v>0.24</v>
+        <v>0.59</v>
       </c>
       <c r="AB9">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AC9">
-        <v>0.38</v>
+        <v>0.63</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="AE9">
         <v>0.15</v>
@@ -18513,13 +18513,13 @@
         <v>0.62</v>
       </c>
       <c r="AG9">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="AH9" t="str">
         <v>ĐẠT</v>
       </c>
       <c r="AI9" t="str">
-        <v/>
+        <v>Đế dùng chung hai bè: hai tai neo</v>
       </c>
     </row>
     <row r="10">
@@ -18551,7 +18551,7 @@
         <v>BÈ 3</v>
       </c>
       <c r="J10">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="K10">
         <v>9.44</v>
@@ -18578,10 +18578,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S10">
-        <v>14.2</v>
+        <v>13.3</v>
       </c>
       <c r="T10">
-        <v>41.6</v>
+        <v>40.7</v>
       </c>
       <c r="U10">
         <v>2.5</v>
@@ -18602,16 +18602,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA10">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="AB10">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="AC10">
-        <v>0.71</v>
+        <v>0.69</v>
       </c>
       <c r="AD10">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="AE10">
         <v>0.15</v>
@@ -18620,7 +18620,7 @@
         <v>0.62</v>
       </c>
       <c r="AG10">
-        <v>0.71</v>
+        <v>0.69</v>
       </c>
       <c r="AH10" t="str">
         <v>ĐẠT</v>
@@ -18658,7 +18658,7 @@
         <v>BÈ 3</v>
       </c>
       <c r="J11">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="K11">
         <v>15.72</v>
@@ -18685,10 +18685,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S11">
-        <v>20.9</v>
+        <v>19.9</v>
       </c>
       <c r="T11">
-        <v>29.3</v>
+        <v>28.6</v>
       </c>
       <c r="U11">
         <v>2.5</v>
@@ -18709,16 +18709,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA11">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="AB11">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="AC11">
-        <v>0.57</v>
+        <v>0.56</v>
       </c>
       <c r="AD11">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="AE11">
         <v>0.15</v>
@@ -18753,7 +18753,7 @@
         <v>BÈ 3</v>
       </c>
       <c r="F12">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="G12">
         <v>9.54</v>
@@ -18792,10 +18792,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S12">
-        <v>32</v>
+        <v>32.9</v>
       </c>
       <c r="T12">
-        <v>68.2</v>
+        <v>67.3</v>
       </c>
       <c r="U12">
         <v>3.25</v>
@@ -18816,16 +18816,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA12">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="AB12">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="AC12">
-        <v>0.94</v>
+        <v>0.93</v>
       </c>
       <c r="AD12">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="AE12">
         <v>0.15</v>
@@ -18834,7 +18834,7 @@
         <v>0.62</v>
       </c>
       <c r="AG12">
-        <v>0.94</v>
+        <v>0.93</v>
       </c>
       <c r="AH12" t="str">
         <v>ĐẠT</v>
@@ -18860,7 +18860,7 @@
         <v>BÈ 3</v>
       </c>
       <c r="F13">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="G13">
         <v>18.74</v>
@@ -18899,40 +18899,40 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S13">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="T13">
-        <v>45.7</v>
+        <v>45.2</v>
       </c>
       <c r="U13">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="V13">
         <v>0.4</v>
       </c>
       <c r="W13">
-        <v>54</v>
+        <v>45.4</v>
       </c>
       <c r="X13">
-        <v>3.58</v>
+        <v>3.01</v>
       </c>
       <c r="Y13">
-        <v>9.2</v>
+        <v>7.7</v>
       </c>
       <c r="Z13" t="str">
         <v>Ø12 a200</v>
       </c>
       <c r="AA13">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AB13">
-        <v>0.63</v>
+        <v>0.69</v>
       </c>
       <c r="AC13">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="AD13">
-        <v>0.54</v>
+        <v>0.84</v>
       </c>
       <c r="AE13">
         <v>0.15</v>
@@ -18941,7 +18941,7 @@
         <v>0.62</v>
       </c>
       <c r="AG13">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="AH13" t="str">
         <v>ĐẠT</v>
@@ -18967,7 +18967,7 @@
         <v>BÈ 3</v>
       </c>
       <c r="F14">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="G14">
         <v>14.3</v>
@@ -19006,10 +19006,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S14">
-        <v>42.7</v>
+        <v>43.1</v>
       </c>
       <c r="T14">
-        <v>55.7</v>
+        <v>55.1</v>
       </c>
       <c r="U14">
         <v>3</v>
@@ -19033,13 +19033,13 @@
         <v>0.69</v>
       </c>
       <c r="AB14">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AC14">
         <v>0.91</v>
       </c>
       <c r="AD14">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="AE14">
         <v>0.15</v>
@@ -19074,7 +19074,7 @@
         <v>BÈ 3</v>
       </c>
       <c r="F15">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="G15">
         <v>9.76</v>
@@ -19113,10 +19113,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S15">
-        <v>57.6</v>
+        <v>57.5</v>
       </c>
       <c r="T15">
-        <v>59.8</v>
+        <v>58.9</v>
       </c>
       <c r="U15">
         <v>3.25</v>
@@ -19137,16 +19137,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA15">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="AB15">
         <v>0.58</v>
       </c>
       <c r="AC15">
-        <v>0.94</v>
+        <v>0.93</v>
       </c>
       <c r="AD15">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AE15">
         <v>0.15</v>
@@ -19155,7 +19155,7 @@
         <v>0.62</v>
       </c>
       <c r="AG15">
-        <v>0.94</v>
+        <v>0.93</v>
       </c>
       <c r="AH15" t="str">
         <v>ĐẠT</v>
@@ -20798,7 +20798,7 @@
         <v>BÈ 6</v>
       </c>
       <c r="J31">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="K31">
         <v>20.76</v>
@@ -20849,10 +20849,10 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA31">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="AB31">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="AC31">
         <v>0.94</v>
@@ -20884,7 +20884,7 @@
         <v>HV-DV026</v>
       </c>
       <c r="C32" t="str">
-        <v>ĐƠN</v>
+        <v>DÙNG CHUNG</v>
       </c>
       <c r="D32" t="str">
         <v>B5A-D14</v>
@@ -20896,31 +20896,31 @@
         <v>87.3</v>
       </c>
       <c r="G32">
-        <v>17.49</v>
+        <v>19.29</v>
       </c>
       <c r="H32" t="str">
-        <v>-</v>
+        <v>B6-D31</v>
       </c>
       <c r="I32" t="str">
-        <v>-</v>
-      </c>
-      <c r="J32" t="str">
-        <v>-</v>
-      </c>
-      <c r="K32" t="str">
-        <v>-</v>
+        <v>BÈ 6</v>
+      </c>
+      <c r="J32">
+        <v>40.8</v>
+      </c>
+      <c r="K32">
+        <v>19.28</v>
       </c>
       <c r="L32">
-        <v>351.47</v>
+        <v>354.71</v>
       </c>
       <c r="M32">
-        <v>-77.42</v>
+        <v>-75.89</v>
       </c>
       <c r="N32">
         <v>378.3</v>
       </c>
       <c r="O32">
-        <v>381.07</v>
+        <v>381.12</v>
       </c>
       <c r="P32">
         <v>1.7</v>
@@ -20929,13 +20929,13 @@
         <v>7.7</v>
       </c>
       <c r="R32" t="str">
-        <v>B5A-D14 căng (MN cao)</v>
+        <v>B5A-D14 căng, B6-D31 chùng (MN cao)</v>
       </c>
       <c r="S32">
-        <v>80.8</v>
+        <v>77.2</v>
       </c>
       <c r="T32">
-        <v>33</v>
+        <v>32.1</v>
       </c>
       <c r="U32">
         <v>2.75</v>
@@ -20956,16 +20956,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA32">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="AB32">
-        <v>0.86</v>
+        <v>0.81</v>
       </c>
       <c r="AC32">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AD32">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
       <c r="AE32">
         <v>0.15</v>
@@ -20974,13 +20974,13 @@
         <v>0.62</v>
       </c>
       <c r="AG32">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AH32" t="str">
         <v>ĐẠT</v>
       </c>
       <c r="AI32" t="str">
-        <v>Địa hình IFC tại điểm này cao hơn đáy thiết kế 2,8 m: kiểm tra khảo sát / nạo vét trước khi đặt đế; Đế lớn hơn đế mẫu</v>
+        <v>Đế dùng chung hai bè: hai tai neo; Địa hình IFC tại điểm này cao hơn đáy thiết kế 2,8 m: kiểm tra khảo sát / nạo vét trước khi đặt đế; Đế lớn hơn đế mẫu</v>
       </c>
     </row>
     <row r="33">
@@ -21012,7 +21012,7 @@
         <v>BÈ 6</v>
       </c>
       <c r="J33">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="K33">
         <v>22.08</v>
@@ -21039,10 +21039,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S33">
-        <v>67.2</v>
+        <v>67.4</v>
       </c>
       <c r="T33">
-        <v>36.4</v>
+        <v>36.1</v>
       </c>
       <c r="U33">
         <v>2.75</v>
@@ -21072,7 +21072,7 @@
         <v>0.87</v>
       </c>
       <c r="AD33">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="AE33">
         <v>0.15</v>
@@ -21419,37 +21419,37 @@
         <v>HV-DV031</v>
       </c>
       <c r="C37" t="str">
-        <v>ĐƠN</v>
+        <v>DÙNG CHUNG</v>
       </c>
       <c r="D37" t="str">
+        <v>B7-D33</v>
+      </c>
+      <c r="E37" t="str">
+        <v>BÈ 7</v>
+      </c>
+      <c r="F37">
+        <v>45.6</v>
+      </c>
+      <c r="G37">
+        <v>11.3</v>
+      </c>
+      <c r="H37" t="str">
         <v>B8-D30</v>
       </c>
-      <c r="E37" t="str">
+      <c r="I37" t="str">
         <v>BÈ 8</v>
       </c>
-      <c r="F37">
+      <c r="J37">
         <v>59.1</v>
       </c>
-      <c r="G37">
-        <v>11.25</v>
-      </c>
-      <c r="H37" t="str">
-        <v>-</v>
-      </c>
-      <c r="I37" t="str">
-        <v>-</v>
-      </c>
-      <c r="J37" t="str">
-        <v>-</v>
-      </c>
-      <c r="K37" t="str">
-        <v>-</v>
+      <c r="K37">
+        <v>11.3</v>
       </c>
       <c r="L37">
-        <v>94.4</v>
+        <v>94.38</v>
       </c>
       <c r="M37">
-        <v>90.54</v>
+        <v>90.49</v>
       </c>
       <c r="N37">
         <v>378.3</v>
@@ -21464,13 +21464,13 @@
         <v>7.7</v>
       </c>
       <c r="R37" t="str">
-        <v>B8-D30 căng (MN cao)</v>
+        <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S37">
-        <v>49.9</v>
+        <v>11.5</v>
       </c>
       <c r="T37">
-        <v>31.7</v>
+        <v>56</v>
       </c>
       <c r="U37">
         <v>2.5</v>
@@ -21491,16 +21491,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA37">
-        <v>0.48</v>
+        <v>0.86</v>
       </c>
       <c r="AB37">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="AC37">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="AD37">
-        <v>0.67</v>
+        <v>0.92</v>
       </c>
       <c r="AE37">
         <v>0.15</v>
@@ -21509,13 +21509,13 @@
         <v>0.62</v>
       </c>
       <c r="AG37">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="AH37" t="str">
         <v>ĐẠT</v>
       </c>
       <c r="AI37" t="str">
-        <v/>
+        <v>Đế dùng chung hai bè: hai tai neo</v>
       </c>
     </row>
     <row r="38">
@@ -21651,7 +21651,7 @@
         <v xml:space="preserve">  trong đó đế dùng chung hai bè</v>
       </c>
       <c r="B42">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C42" t="str">
         <v>đế</v>
@@ -21662,7 +21662,7 @@
         <v>Số tuyến cáp neo vào đế</v>
       </c>
       <c r="B43">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C43" t="str">
         <v>tuyến</v>
@@ -21684,7 +21684,7 @@
         <v>Bê tông đế</v>
       </c>
       <c r="B45">
-        <v>94</v>
+        <v>93.4</v>
       </c>
       <c r="C45" t="str">
         <v>m³</v>
@@ -21717,7 +21717,7 @@
         <v>Số đế cạnh B = 2,75 m</v>
       </c>
       <c r="B48">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C48" t="str">
         <v>đế</v>
@@ -21728,7 +21728,7 @@
         <v>Số đế cạnh B = 3,00 m</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49" t="str">
         <v>đế</v>
@@ -24607,16 +24607,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P39">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q39">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="R39">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="S39">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="T39">
         <v>1</v>
@@ -24690,16 +24690,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P40">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q40">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="R40">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="S40">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="T40">
         <v>1</v>
@@ -24773,16 +24773,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P41">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q41">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="R41">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="S41">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="T41">
         <v>1</v>
@@ -24856,16 +24856,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P42">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q42">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="R42">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="S42">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="T42">
         <v>1</v>
@@ -24939,16 +24939,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P43">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q43">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="R43">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="S43">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="T43">
         <v>1</v>
@@ -25022,16 +25022,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P44">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q44">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="R44">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="S44">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="T44">
         <v>1</v>
@@ -25105,16 +25105,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P45">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q45">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="R45">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="S45">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="T45">
         <v>1</v>
@@ -25188,16 +25188,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P46">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q46">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="R46">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="S46">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="T46">
         <v>1</v>
@@ -25271,16 +25271,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P47">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q47">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="R47">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="S47">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="T47">
         <v>1</v>
@@ -25354,16 +25354,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P48">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q48">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="R48">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="S48">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="T48">
         <v>1</v>
@@ -25437,16 +25437,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P49">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q49">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="R49">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="S49">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="T49">
         <v>1</v>
@@ -25520,16 +25520,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P50">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q50">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="R50">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="S50">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="T50">
         <v>1</v>
@@ -25603,16 +25603,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P51">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q51">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="R51">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="S51">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="T51">
         <v>1</v>
@@ -25686,16 +25686,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P52">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q52">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="R52">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="S52">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="T52">
         <v>1</v>
@@ -25769,16 +25769,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P53">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="Q53">
-        <v>40.1</v>
+        <v>38.6</v>
       </c>
       <c r="R53">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="S53">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="T53">
         <v>1</v>
@@ -25810,7 +25810,7 @@
         <v>48</v>
       </c>
       <c r="B54" t="str">
-        <v>HV-P061</v>
+        <v>HV-P062</v>
       </c>
       <c r="C54" t="str">
         <v>B3A-D01</v>
@@ -25893,7 +25893,7 @@
         <v>49</v>
       </c>
       <c r="B55" t="str">
-        <v>HV-P062</v>
+        <v>HV-P063</v>
       </c>
       <c r="C55" t="str">
         <v>B3A-D02</v>
@@ -25976,7 +25976,7 @@
         <v>50</v>
       </c>
       <c r="B56" t="str">
-        <v>HV-P063</v>
+        <v>HV-P064</v>
       </c>
       <c r="C56" t="str">
         <v>B3A-D03</v>
@@ -26059,7 +26059,7 @@
         <v>51</v>
       </c>
       <c r="B57" t="str">
-        <v>HV-P064</v>
+        <v>HV-P065</v>
       </c>
       <c r="C57" t="str">
         <v>B3A-D04</v>
@@ -26142,7 +26142,7 @@
         <v>52</v>
       </c>
       <c r="B58" t="str">
-        <v>HV-P065</v>
+        <v>HV-P066</v>
       </c>
       <c r="C58" t="str">
         <v>B3A-D05</v>
@@ -26225,7 +26225,7 @@
         <v>53</v>
       </c>
       <c r="B59" t="str">
-        <v>HV-P066</v>
+        <v>HV-P067</v>
       </c>
       <c r="C59" t="str">
         <v>B3A-D06</v>
@@ -26308,7 +26308,7 @@
         <v>54</v>
       </c>
       <c r="B60" t="str">
-        <v>HV-P067</v>
+        <v>HV-P068</v>
       </c>
       <c r="C60" t="str">
         <v>B3A-D07</v>
@@ -26391,7 +26391,7 @@
         <v>55</v>
       </c>
       <c r="B61" t="str">
-        <v>HV-P068</v>
+        <v>HV-P069</v>
       </c>
       <c r="C61" t="str">
         <v>B3A-D08</v>
@@ -26474,7 +26474,7 @@
         <v>56</v>
       </c>
       <c r="B62" t="str">
-        <v>HV-P069</v>
+        <v>HV-P070</v>
       </c>
       <c r="C62" t="str">
         <v>B3A-D09</v>
@@ -26557,7 +26557,7 @@
         <v>57</v>
       </c>
       <c r="B63" t="str">
-        <v>HV-P070</v>
+        <v>HV-P071</v>
       </c>
       <c r="C63" t="str">
         <v>B3A-D10</v>
@@ -26640,7 +26640,7 @@
         <v>58</v>
       </c>
       <c r="B64" t="str">
-        <v>HV-P071</v>
+        <v>HV-P072</v>
       </c>
       <c r="C64" t="str">
         <v>B3A-D11</v>
@@ -26723,7 +26723,7 @@
         <v>59</v>
       </c>
       <c r="B65" t="str">
-        <v>HV-P072</v>
+        <v>HV-P073</v>
       </c>
       <c r="C65" t="str">
         <v>B3A-D12</v>
@@ -26806,7 +26806,7 @@
         <v>60</v>
       </c>
       <c r="B66" t="str">
-        <v>HV-P073</v>
+        <v>HV-P074</v>
       </c>
       <c r="C66" t="str">
         <v>B3A-D13</v>
@@ -26889,7 +26889,7 @@
         <v>61</v>
       </c>
       <c r="B67" t="str">
-        <v>HV-P074</v>
+        <v>HV-P075</v>
       </c>
       <c r="C67" t="str">
         <v>B3A-D14</v>
@@ -26972,7 +26972,7 @@
         <v>62</v>
       </c>
       <c r="B68" t="str">
-        <v>HV-P075</v>
+        <v>HV-P076</v>
       </c>
       <c r="C68" t="str">
         <v>B3A-D15</v>
@@ -27055,7 +27055,7 @@
         <v>63</v>
       </c>
       <c r="B69" t="str">
-        <v>HV-P076</v>
+        <v>HV-P077</v>
       </c>
       <c r="C69" t="str">
         <v>B3A-D16</v>
@@ -27138,7 +27138,7 @@
         <v>64</v>
       </c>
       <c r="B70" t="str">
-        <v>HV-P077</v>
+        <v>HV-P078</v>
       </c>
       <c r="C70" t="str">
         <v>B3A-D17</v>
@@ -27221,7 +27221,7 @@
         <v>65</v>
       </c>
       <c r="B71" t="str">
-        <v>HV-P078</v>
+        <v>HV-P079</v>
       </c>
       <c r="C71" t="str">
         <v>B3A-D18</v>
@@ -27304,7 +27304,7 @@
         <v>66</v>
       </c>
       <c r="B72" t="str">
-        <v>HV-P079</v>
+        <v>HV-P080</v>
       </c>
       <c r="C72" t="str">
         <v>B3A-D19</v>
@@ -27387,7 +27387,7 @@
         <v>67</v>
       </c>
       <c r="B73" t="str">
-        <v>HV-P080</v>
+        <v>HV-P081</v>
       </c>
       <c r="C73" t="str">
         <v>B3A-D20</v>
@@ -27470,7 +27470,7 @@
         <v>68</v>
       </c>
       <c r="B74" t="str">
-        <v>HV-P085</v>
+        <v>HV-P086</v>
       </c>
       <c r="C74" t="str">
         <v>B3A-D25</v>
@@ -27553,7 +27553,7 @@
         <v>69</v>
       </c>
       <c r="B75" t="str">
-        <v>HV-P086</v>
+        <v>HV-P087</v>
       </c>
       <c r="C75" t="str">
         <v>B3A-D26</v>
@@ -27636,7 +27636,7 @@
         <v>70</v>
       </c>
       <c r="B76" t="str">
-        <v>HV-P087</v>
+        <v>HV-P088</v>
       </c>
       <c r="C76" t="str">
         <v>B3A-D27</v>
@@ -27719,7 +27719,7 @@
         <v>71</v>
       </c>
       <c r="B77" t="str">
-        <v>HV-P088</v>
+        <v>HV-P089</v>
       </c>
       <c r="C77" t="str">
         <v>B3A-D28</v>
@@ -27802,7 +27802,7 @@
         <v>72</v>
       </c>
       <c r="B78" t="str">
-        <v>HV-P089</v>
+        <v>HV-P090</v>
       </c>
       <c r="C78" t="str">
         <v>B3A-D29</v>
@@ -27885,7 +27885,7 @@
         <v>73</v>
       </c>
       <c r="B79" t="str">
-        <v>HV-P090</v>
+        <v>HV-P091</v>
       </c>
       <c r="C79" t="str">
         <v>B3A-D30</v>
@@ -27968,7 +27968,7 @@
         <v>74</v>
       </c>
       <c r="B80" t="str">
-        <v>HV-P091</v>
+        <v>HV-P092</v>
       </c>
       <c r="C80" t="str">
         <v>B3A-D31</v>
@@ -28051,7 +28051,7 @@
         <v>75</v>
       </c>
       <c r="B81" t="str">
-        <v>HV-P092</v>
+        <v>HV-P093</v>
       </c>
       <c r="C81" t="str">
         <v>B3A-D32</v>
@@ -28134,7 +28134,7 @@
         <v>76</v>
       </c>
       <c r="B82" t="str">
-        <v>HV-P093</v>
+        <v>HV-P094</v>
       </c>
       <c r="C82" t="str">
         <v>B3A-D33</v>
@@ -28217,7 +28217,7 @@
         <v>77</v>
       </c>
       <c r="B83" t="str">
-        <v>HV-P094</v>
+        <v>HV-P095</v>
       </c>
       <c r="C83" t="str">
         <v>B3A-D34</v>
@@ -28300,7 +28300,7 @@
         <v>78</v>
       </c>
       <c r="B84" t="str">
-        <v>HV-P095</v>
+        <v>HV-P096</v>
       </c>
       <c r="C84" t="str">
         <v>B3A-D35</v>
@@ -28383,7 +28383,7 @@
         <v>79</v>
       </c>
       <c r="B85" t="str">
-        <v>HV-P111</v>
+        <v>HV-P112</v>
       </c>
       <c r="C85" t="str">
         <v>B5A-D01</v>
@@ -28466,7 +28466,7 @@
         <v>80</v>
       </c>
       <c r="B86" t="str">
-        <v>HV-P112</v>
+        <v>HV-P113</v>
       </c>
       <c r="C86" t="str">
         <v>B5A-D02</v>
@@ -28549,7 +28549,7 @@
         <v>81</v>
       </c>
       <c r="B87" t="str">
-        <v>HV-P113</v>
+        <v>HV-P114</v>
       </c>
       <c r="C87" t="str">
         <v>B5A-D03</v>
@@ -28632,7 +28632,7 @@
         <v>82</v>
       </c>
       <c r="B88" t="str">
-        <v>HV-P114</v>
+        <v>HV-P115</v>
       </c>
       <c r="C88" t="str">
         <v>B5A-D04</v>
@@ -28715,7 +28715,7 @@
         <v>83</v>
       </c>
       <c r="B89" t="str">
-        <v>HV-P115</v>
+        <v>HV-P116</v>
       </c>
       <c r="C89" t="str">
         <v>B5A-D05</v>
@@ -28798,7 +28798,7 @@
         <v>84</v>
       </c>
       <c r="B90" t="str">
-        <v>HV-P116</v>
+        <v>HV-P117</v>
       </c>
       <c r="C90" t="str">
         <v>B5A-D06</v>
@@ -28881,7 +28881,7 @@
         <v>85</v>
       </c>
       <c r="B91" t="str">
-        <v>HV-P117</v>
+        <v>HV-P118</v>
       </c>
       <c r="C91" t="str">
         <v>B5A-D07</v>
@@ -28964,7 +28964,7 @@
         <v>86</v>
       </c>
       <c r="B92" t="str">
-        <v>HV-P118</v>
+        <v>HV-P119</v>
       </c>
       <c r="C92" t="str">
         <v>B5A-D08</v>
@@ -29047,7 +29047,7 @@
         <v>87</v>
       </c>
       <c r="B93" t="str">
-        <v>HV-P119</v>
+        <v>HV-P120</v>
       </c>
       <c r="C93" t="str">
         <v>B5A-D09</v>
@@ -29130,7 +29130,7 @@
         <v>88</v>
       </c>
       <c r="B94" t="str">
-        <v>HV-P120</v>
+        <v>HV-P121</v>
       </c>
       <c r="C94" t="str">
         <v>B5A-D10</v>
@@ -29213,7 +29213,7 @@
         <v>89</v>
       </c>
       <c r="B95" t="str">
-        <v>HV-P121</v>
+        <v>HV-P122</v>
       </c>
       <c r="C95" t="str">
         <v>B5A-D11</v>
@@ -29296,7 +29296,7 @@
         <v>90</v>
       </c>
       <c r="B96" t="str">
-        <v>HV-P122</v>
+        <v>HV-P123</v>
       </c>
       <c r="C96" t="str">
         <v>B5A-D12</v>
@@ -29379,7 +29379,7 @@
         <v>91</v>
       </c>
       <c r="B97" t="str">
-        <v>HV-P126</v>
+        <v>HV-P127</v>
       </c>
       <c r="C97" t="str">
         <v>B5A-D16</v>
@@ -29462,7 +29462,7 @@
         <v>92</v>
       </c>
       <c r="B98" t="str">
-        <v>HV-P127</v>
+        <v>HV-P128</v>
       </c>
       <c r="C98" t="str">
         <v>B5A-D17</v>
@@ -29545,7 +29545,7 @@
         <v>93</v>
       </c>
       <c r="B99" t="str">
-        <v>HV-P128</v>
+        <v>HV-P129</v>
       </c>
       <c r="C99" t="str">
         <v>B5A-D18</v>
@@ -29628,7 +29628,7 @@
         <v>94</v>
       </c>
       <c r="B100" t="str">
-        <v>HV-P129</v>
+        <v>HV-P130</v>
       </c>
       <c r="C100" t="str">
         <v>B5A-D19</v>
@@ -29711,7 +29711,7 @@
         <v>95</v>
       </c>
       <c r="B101" t="str">
-        <v>HV-P130</v>
+        <v>HV-P131</v>
       </c>
       <c r="C101" t="str">
         <v>B5A-D20</v>
@@ -29794,7 +29794,7 @@
         <v>96</v>
       </c>
       <c r="B102" t="str">
-        <v>HV-P131</v>
+        <v>HV-P132</v>
       </c>
       <c r="C102" t="str">
         <v>B5A-D21</v>
@@ -29877,7 +29877,7 @@
         <v>97</v>
       </c>
       <c r="B103" t="str">
-        <v>HV-P132</v>
+        <v>HV-P133</v>
       </c>
       <c r="C103" t="str">
         <v>B5A-D22</v>
@@ -29960,7 +29960,7 @@
         <v>98</v>
       </c>
       <c r="B104" t="str">
-        <v>HV-P143</v>
+        <v>HV-P144</v>
       </c>
       <c r="C104" t="str">
         <v>B5A-D33</v>
@@ -30043,7 +30043,7 @@
         <v>99</v>
       </c>
       <c r="B105" t="str">
-        <v>HV-P144</v>
+        <v>HV-P145</v>
       </c>
       <c r="C105" t="str">
         <v>B5A-D34</v>
@@ -30126,7 +30126,7 @@
         <v>100</v>
       </c>
       <c r="B106" t="str">
-        <v>HV-P145</v>
+        <v>HV-P146</v>
       </c>
       <c r="C106" t="str">
         <v>B5A-D35</v>
@@ -30209,7 +30209,7 @@
         <v>101</v>
       </c>
       <c r="B107" t="str">
-        <v>HV-P146</v>
+        <v>HV-P147</v>
       </c>
       <c r="C107" t="str">
         <v>B5A-D36</v>
@@ -30292,7 +30292,7 @@
         <v>102</v>
       </c>
       <c r="B108" t="str">
-        <v>HV-P147</v>
+        <v>HV-P148</v>
       </c>
       <c r="C108" t="str">
         <v>B5A-D37</v>
@@ -30375,7 +30375,7 @@
         <v>103</v>
       </c>
       <c r="B109" t="str">
-        <v>HV-P148</v>
+        <v>HV-P149</v>
       </c>
       <c r="C109" t="str">
         <v>B5A-D38</v>
@@ -30458,7 +30458,7 @@
         <v>104</v>
       </c>
       <c r="B110" t="str">
-        <v>HV-P149</v>
+        <v>HV-P150</v>
       </c>
       <c r="C110" t="str">
         <v>B5A-D39</v>
@@ -30541,7 +30541,7 @@
         <v>105</v>
       </c>
       <c r="B111" t="str">
-        <v>HV-P150</v>
+        <v>HV-P151</v>
       </c>
       <c r="C111" t="str">
         <v>B5A-D40</v>
@@ -30624,7 +30624,7 @@
         <v>106</v>
       </c>
       <c r="B112" t="str">
-        <v>HV-P151</v>
+        <v>HV-P152</v>
       </c>
       <c r="C112" t="str">
         <v>B5A-D41</v>
@@ -30707,7 +30707,7 @@
         <v>107</v>
       </c>
       <c r="B113" t="str">
-        <v>HV-P152</v>
+        <v>HV-P153</v>
       </c>
       <c r="C113" t="str">
         <v>B5A-D42</v>
@@ -30790,7 +30790,7 @@
         <v>108</v>
       </c>
       <c r="B114" t="str">
-        <v>HV-P153</v>
+        <v>HV-P154</v>
       </c>
       <c r="C114" t="str">
         <v>B5A-D43</v>
@@ -30873,7 +30873,7 @@
         <v>109</v>
       </c>
       <c r="B115" t="str">
-        <v>HV-P154</v>
+        <v>HV-P155</v>
       </c>
       <c r="C115" t="str">
         <v>B5A-D44</v>
@@ -30956,7 +30956,7 @@
         <v>110</v>
       </c>
       <c r="B116" t="str">
-        <v>HV-P155</v>
+        <v>HV-P156</v>
       </c>
       <c r="C116" t="str">
         <v>B5A-D45</v>
@@ -31039,7 +31039,7 @@
         <v>111</v>
       </c>
       <c r="B117" t="str">
-        <v>HV-P156</v>
+        <v>HV-P157</v>
       </c>
       <c r="C117" t="str">
         <v>B5A-D46</v>
@@ -31122,7 +31122,7 @@
         <v>112</v>
       </c>
       <c r="B118" t="str">
-        <v>HV-P157</v>
+        <v>HV-P158</v>
       </c>
       <c r="C118" t="str">
         <v>B5A-D47</v>
@@ -31205,7 +31205,7 @@
         <v>113</v>
       </c>
       <c r="B119" t="str">
-        <v>HV-P158</v>
+        <v>HV-P159</v>
       </c>
       <c r="C119" t="str">
         <v>B5A-D48</v>
@@ -31288,7 +31288,7 @@
         <v>114</v>
       </c>
       <c r="B120" t="str">
-        <v>HV-P159</v>
+        <v>HV-P160</v>
       </c>
       <c r="C120" t="str">
         <v>B5A-D49</v>
@@ -31371,7 +31371,7 @@
         <v>115</v>
       </c>
       <c r="B121" t="str">
-        <v>HV-P160</v>
+        <v>HV-P161</v>
       </c>
       <c r="C121" t="str">
         <v>B6-D01</v>
@@ -31413,16 +31413,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P121">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q121">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R121">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S121">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T121">
         <v>1</v>
@@ -31454,7 +31454,7 @@
         <v>116</v>
       </c>
       <c r="B122" t="str">
-        <v>HV-P161</v>
+        <v>HV-P162</v>
       </c>
       <c r="C122" t="str">
         <v>B6-D02</v>
@@ -31496,16 +31496,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P122">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q122">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R122">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S122">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T122">
         <v>1</v>
@@ -31537,7 +31537,7 @@
         <v>117</v>
       </c>
       <c r="B123" t="str">
-        <v>HV-P162</v>
+        <v>HV-P163</v>
       </c>
       <c r="C123" t="str">
         <v>B6-D03</v>
@@ -31579,16 +31579,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P123">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q123">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R123">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S123">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T123">
         <v>1</v>
@@ -31620,7 +31620,7 @@
         <v>118</v>
       </c>
       <c r="B124" t="str">
-        <v>HV-P163</v>
+        <v>HV-P164</v>
       </c>
       <c r="C124" t="str">
         <v>B6-D04</v>
@@ -31662,16 +31662,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P124">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q124">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R124">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S124">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T124">
         <v>1</v>
@@ -31703,7 +31703,7 @@
         <v>119</v>
       </c>
       <c r="B125" t="str">
-        <v>HV-P164</v>
+        <v>HV-P165</v>
       </c>
       <c r="C125" t="str">
         <v>B6-D05</v>
@@ -31745,16 +31745,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P125">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q125">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R125">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S125">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T125">
         <v>1</v>
@@ -31786,7 +31786,7 @@
         <v>120</v>
       </c>
       <c r="B126" t="str">
-        <v>HV-P165</v>
+        <v>HV-P166</v>
       </c>
       <c r="C126" t="str">
         <v>B6-D06</v>
@@ -31828,16 +31828,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P126">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q126">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R126">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S126">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T126">
         <v>1</v>
@@ -31869,7 +31869,7 @@
         <v>121</v>
       </c>
       <c r="B127" t="str">
-        <v>HV-P166</v>
+        <v>HV-P167</v>
       </c>
       <c r="C127" t="str">
         <v>B6-D07</v>
@@ -31911,16 +31911,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P127">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q127">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R127">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S127">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T127">
         <v>1</v>
@@ -31952,7 +31952,7 @@
         <v>122</v>
       </c>
       <c r="B128" t="str">
-        <v>HV-P167</v>
+        <v>HV-P168</v>
       </c>
       <c r="C128" t="str">
         <v>B6-D08</v>
@@ -31994,16 +31994,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P128">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q128">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R128">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S128">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T128">
         <v>1</v>
@@ -32035,7 +32035,7 @@
         <v>123</v>
       </c>
       <c r="B129" t="str">
-        <v>HV-P168</v>
+        <v>HV-P169</v>
       </c>
       <c r="C129" t="str">
         <v>B6-D09</v>
@@ -32077,16 +32077,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P129">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q129">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R129">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S129">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T129">
         <v>1</v>
@@ -32118,7 +32118,7 @@
         <v>124</v>
       </c>
       <c r="B130" t="str">
-        <v>HV-P169</v>
+        <v>HV-P170</v>
       </c>
       <c r="C130" t="str">
         <v>B6-D10</v>
@@ -32160,16 +32160,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P130">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q130">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R130">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S130">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T130">
         <v>1</v>
@@ -32201,7 +32201,7 @@
         <v>125</v>
       </c>
       <c r="B131" t="str">
-        <v>HV-P170</v>
+        <v>HV-P171</v>
       </c>
       <c r="C131" t="str">
         <v>B6-D11</v>
@@ -32243,16 +32243,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P131">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q131">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R131">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S131">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T131">
         <v>1</v>
@@ -32284,7 +32284,7 @@
         <v>126</v>
       </c>
       <c r="B132" t="str">
-        <v>HV-P171</v>
+        <v>HV-P172</v>
       </c>
       <c r="C132" t="str">
         <v>B6-D12</v>
@@ -32326,16 +32326,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P132">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q132">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R132">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S132">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T132">
         <v>1</v>
@@ -32367,7 +32367,7 @@
         <v>127</v>
       </c>
       <c r="B133" t="str">
-        <v>HV-P172</v>
+        <v>HV-P173</v>
       </c>
       <c r="C133" t="str">
         <v>B6-D13</v>
@@ -32409,16 +32409,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P133">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q133">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R133">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S133">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T133">
         <v>1</v>
@@ -32450,7 +32450,7 @@
         <v>128</v>
       </c>
       <c r="B134" t="str">
-        <v>HV-P173</v>
+        <v>HV-P174</v>
       </c>
       <c r="C134" t="str">
         <v>B6-D14</v>
@@ -32492,16 +32492,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P134">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q134">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R134">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S134">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T134">
         <v>1</v>
@@ -32533,7 +32533,7 @@
         <v>129</v>
       </c>
       <c r="B135" t="str">
-        <v>HV-P174</v>
+        <v>HV-P175</v>
       </c>
       <c r="C135" t="str">
         <v>B6-D15</v>
@@ -32575,16 +32575,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P135">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q135">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R135">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S135">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T135">
         <v>1</v>
@@ -32616,7 +32616,7 @@
         <v>130</v>
       </c>
       <c r="B136" t="str">
-        <v>HV-P175</v>
+        <v>HV-P176</v>
       </c>
       <c r="C136" t="str">
         <v>B6-D16</v>
@@ -32658,16 +32658,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P136">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q136">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R136">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S136">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T136">
         <v>1</v>
@@ -32699,7 +32699,7 @@
         <v>131</v>
       </c>
       <c r="B137" t="str">
-        <v>HV-P177</v>
+        <v>HV-P178</v>
       </c>
       <c r="C137" t="str">
         <v>B6-D18</v>
@@ -32741,16 +32741,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P137">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q137">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R137">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S137">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T137">
         <v>1</v>
@@ -32782,7 +32782,7 @@
         <v>132</v>
       </c>
       <c r="B138" t="str">
-        <v>HV-P178</v>
+        <v>HV-P179</v>
       </c>
       <c r="C138" t="str">
         <v>B6-D19</v>
@@ -32824,16 +32824,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P138">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q138">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R138">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S138">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T138">
         <v>1</v>
@@ -32865,7 +32865,7 @@
         <v>133</v>
       </c>
       <c r="B139" t="str">
-        <v>HV-P179</v>
+        <v>HV-P180</v>
       </c>
       <c r="C139" t="str">
         <v>B6-D20</v>
@@ -32907,16 +32907,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P139">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q139">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R139">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S139">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T139">
         <v>1</v>
@@ -32948,7 +32948,7 @@
         <v>134</v>
       </c>
       <c r="B140" t="str">
-        <v>HV-P180</v>
+        <v>HV-P181</v>
       </c>
       <c r="C140" t="str">
         <v>B6-D21</v>
@@ -32990,16 +32990,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P140">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q140">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R140">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S140">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T140">
         <v>1</v>
@@ -33031,7 +33031,7 @@
         <v>135</v>
       </c>
       <c r="B141" t="str">
-        <v>HV-P181</v>
+        <v>HV-P182</v>
       </c>
       <c r="C141" t="str">
         <v>B6-D22</v>
@@ -33073,16 +33073,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P141">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q141">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R141">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S141">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T141">
         <v>1</v>
@@ -33114,7 +33114,7 @@
         <v>136</v>
       </c>
       <c r="B142" t="str">
-        <v>HV-P182</v>
+        <v>HV-P183</v>
       </c>
       <c r="C142" t="str">
         <v>B6-D23</v>
@@ -33156,16 +33156,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P142">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q142">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R142">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S142">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T142">
         <v>1</v>
@@ -33197,7 +33197,7 @@
         <v>137</v>
       </c>
       <c r="B143" t="str">
-        <v>HV-P183</v>
+        <v>HV-P184</v>
       </c>
       <c r="C143" t="str">
         <v>B6-D24</v>
@@ -33239,16 +33239,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P143">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q143">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R143">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S143">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T143">
         <v>1</v>
@@ -33280,7 +33280,7 @@
         <v>138</v>
       </c>
       <c r="B144" t="str">
-        <v>HV-P184</v>
+        <v>HV-P185</v>
       </c>
       <c r="C144" t="str">
         <v>B6-D25</v>
@@ -33322,16 +33322,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P144">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q144">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R144">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S144">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T144">
         <v>1</v>
@@ -33363,7 +33363,7 @@
         <v>139</v>
       </c>
       <c r="B145" t="str">
-        <v>HV-P185</v>
+        <v>HV-P186</v>
       </c>
       <c r="C145" t="str">
         <v>B6-D26</v>
@@ -33405,16 +33405,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P145">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q145">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R145">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S145">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T145">
         <v>1</v>
@@ -33446,7 +33446,7 @@
         <v>140</v>
       </c>
       <c r="B146" t="str">
-        <v>HV-P187</v>
+        <v>HV-P188</v>
       </c>
       <c r="C146" t="str">
         <v>B6-D28</v>
@@ -33488,16 +33488,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P146">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q146">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R146">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S146">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T146">
         <v>1</v>
@@ -33529,7 +33529,7 @@
         <v>141</v>
       </c>
       <c r="B147" t="str">
-        <v>HV-P188</v>
+        <v>HV-P189</v>
       </c>
       <c r="C147" t="str">
         <v>B6-D29</v>
@@ -33571,16 +33571,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P147">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q147">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R147">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S147">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T147">
         <v>1</v>
@@ -33612,7 +33612,7 @@
         <v>142</v>
       </c>
       <c r="B148" t="str">
-        <v>HV-P189</v>
+        <v>HV-P190</v>
       </c>
       <c r="C148" t="str">
         <v>B6-D30</v>
@@ -33654,16 +33654,16 @@
         <v>CB400-V</v>
       </c>
       <c r="P148">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="Q148">
-        <v>41.9</v>
+        <v>40.8</v>
       </c>
       <c r="R148">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="S148">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="T148">
         <v>1</v>
@@ -33695,7 +33695,7 @@
         <v>143</v>
       </c>
       <c r="B149" t="str">
-        <v>HV-P190</v>
+        <v>HV-P192</v>
       </c>
       <c r="C149" t="str">
         <v>B7-D01</v>
@@ -33778,7 +33778,7 @@
         <v>144</v>
       </c>
       <c r="B150" t="str">
-        <v>HV-P191</v>
+        <v>HV-P193</v>
       </c>
       <c r="C150" t="str">
         <v>B7-D02</v>
@@ -33861,7 +33861,7 @@
         <v>145</v>
       </c>
       <c r="B151" t="str">
-        <v>HV-P192</v>
+        <v>HV-P194</v>
       </c>
       <c r="C151" t="str">
         <v>B7-D03</v>
@@ -33944,7 +33944,7 @@
         <v>146</v>
       </c>
       <c r="B152" t="str">
-        <v>HV-P193</v>
+        <v>HV-P195</v>
       </c>
       <c r="C152" t="str">
         <v>B7-D04</v>
@@ -34027,7 +34027,7 @@
         <v>147</v>
       </c>
       <c r="B153" t="str">
-        <v>HV-P194</v>
+        <v>HV-P196</v>
       </c>
       <c r="C153" t="str">
         <v>B7-D05</v>
@@ -34110,7 +34110,7 @@
         <v>148</v>
       </c>
       <c r="B154" t="str">
-        <v>HV-P195</v>
+        <v>HV-P197</v>
       </c>
       <c r="C154" t="str">
         <v>B7-D06</v>
@@ -34193,7 +34193,7 @@
         <v>149</v>
       </c>
       <c r="B155" t="str">
-        <v>HV-P196</v>
+        <v>HV-P198</v>
       </c>
       <c r="C155" t="str">
         <v>B7-D07</v>
@@ -34276,7 +34276,7 @@
         <v>150</v>
       </c>
       <c r="B156" t="str">
-        <v>HV-P197</v>
+        <v>HV-P199</v>
       </c>
       <c r="C156" t="str">
         <v>B7-D08</v>
@@ -34359,7 +34359,7 @@
         <v>151</v>
       </c>
       <c r="B157" t="str">
-        <v>HV-P198</v>
+        <v>HV-P200</v>
       </c>
       <c r="C157" t="str">
         <v>B7-D09</v>
@@ -34442,7 +34442,7 @@
         <v>152</v>
       </c>
       <c r="B158" t="str">
-        <v>HV-P199</v>
+        <v>HV-P201</v>
       </c>
       <c r="C158" t="str">
         <v>B7-D10</v>
@@ -34525,7 +34525,7 @@
         <v>153</v>
       </c>
       <c r="B159" t="str">
-        <v>HV-P200</v>
+        <v>HV-P202</v>
       </c>
       <c r="C159" t="str">
         <v>B7-D11</v>
@@ -34608,7 +34608,7 @@
         <v>154</v>
       </c>
       <c r="B160" t="str">
-        <v>HV-P201</v>
+        <v>HV-P203</v>
       </c>
       <c r="C160" t="str">
         <v>B7-D12</v>
@@ -34691,7 +34691,7 @@
         <v>155</v>
       </c>
       <c r="B161" t="str">
-        <v>HV-P202</v>
+        <v>HV-P204</v>
       </c>
       <c r="C161" t="str">
         <v>B7-D13</v>
@@ -34774,7 +34774,7 @@
         <v>156</v>
       </c>
       <c r="B162" t="str">
-        <v>HV-P203</v>
+        <v>HV-P205</v>
       </c>
       <c r="C162" t="str">
         <v>B7-D14</v>
@@ -34857,7 +34857,7 @@
         <v>157</v>
       </c>
       <c r="B163" t="str">
-        <v>HV-P204</v>
+        <v>HV-P206</v>
       </c>
       <c r="C163" t="str">
         <v>B7-D15</v>
@@ -34940,7 +34940,7 @@
         <v>158</v>
       </c>
       <c r="B164" t="str">
-        <v>HV-P205</v>
+        <v>HV-P207</v>
       </c>
       <c r="C164" t="str">
         <v>B7-D16</v>
@@ -35023,7 +35023,7 @@
         <v>159</v>
       </c>
       <c r="B165" t="str">
-        <v>HV-P206</v>
+        <v>HV-P208</v>
       </c>
       <c r="C165" t="str">
         <v>B7-D17</v>
@@ -35106,7 +35106,7 @@
         <v>160</v>
       </c>
       <c r="B166" t="str">
-        <v>HV-P207</v>
+        <v>HV-P209</v>
       </c>
       <c r="C166" t="str">
         <v>B7-D18</v>
@@ -35189,7 +35189,7 @@
         <v>161</v>
       </c>
       <c r="B167" t="str">
-        <v>HV-P210</v>
+        <v>HV-P212</v>
       </c>
       <c r="C167" t="str">
         <v>B7-D21</v>
@@ -35272,7 +35272,7 @@
         <v>162</v>
       </c>
       <c r="B168" t="str">
-        <v>HV-P215</v>
+        <v>HV-P217</v>
       </c>
       <c r="C168" t="str">
         <v>B7-D26</v>
@@ -35355,7 +35355,7 @@
         <v>163</v>
       </c>
       <c r="B169" t="str">
-        <v>HV-P216</v>
+        <v>HV-P218</v>
       </c>
       <c r="C169" t="str">
         <v>B7-D27</v>
@@ -35438,7 +35438,7 @@
         <v>164</v>
       </c>
       <c r="B170" t="str">
-        <v>HV-P217</v>
+        <v>HV-P219</v>
       </c>
       <c r="C170" t="str">
         <v>B7-D28</v>
@@ -35521,7 +35521,7 @@
         <v>165</v>
       </c>
       <c r="B171" t="str">
-        <v>HV-P218</v>
+        <v>HV-P220</v>
       </c>
       <c r="C171" t="str">
         <v>B7-D29</v>
@@ -35604,7 +35604,7 @@
         <v>166</v>
       </c>
       <c r="B172" t="str">
-        <v>HV-P219</v>
+        <v>HV-P221</v>
       </c>
       <c r="C172" t="str">
         <v>B7-D30</v>
@@ -35687,7 +35687,7 @@
         <v>167</v>
       </c>
       <c r="B173" t="str">
-        <v>HV-P222</v>
+        <v>HV-P225</v>
       </c>
       <c r="C173" t="str">
         <v>B8-D01</v>
@@ -35770,7 +35770,7 @@
         <v>168</v>
       </c>
       <c r="B174" t="str">
-        <v>HV-P223</v>
+        <v>HV-P226</v>
       </c>
       <c r="C174" t="str">
         <v>B8-D02</v>
@@ -35853,7 +35853,7 @@
         <v>169</v>
       </c>
       <c r="B175" t="str">
-        <v>HV-P224</v>
+        <v>HV-P227</v>
       </c>
       <c r="C175" t="str">
         <v>B8-D03</v>
@@ -35936,7 +35936,7 @@
         <v>170</v>
       </c>
       <c r="B176" t="str">
-        <v>HV-P225</v>
+        <v>HV-P228</v>
       </c>
       <c r="C176" t="str">
         <v>B8-D04</v>
@@ -36019,7 +36019,7 @@
         <v>171</v>
       </c>
       <c r="B177" t="str">
-        <v>HV-P226</v>
+        <v>HV-P229</v>
       </c>
       <c r="C177" t="str">
         <v>B8-D05</v>
@@ -36102,7 +36102,7 @@
         <v>172</v>
       </c>
       <c r="B178" t="str">
-        <v>HV-P227</v>
+        <v>HV-P230</v>
       </c>
       <c r="C178" t="str">
         <v>B8-D06</v>
@@ -36185,7 +36185,7 @@
         <v>173</v>
       </c>
       <c r="B179" t="str">
-        <v>HV-P228</v>
+        <v>HV-P231</v>
       </c>
       <c r="C179" t="str">
         <v>B8-D07</v>
@@ -36268,7 +36268,7 @@
         <v>174</v>
       </c>
       <c r="B180" t="str">
-        <v>HV-P229</v>
+        <v>HV-P232</v>
       </c>
       <c r="C180" t="str">
         <v>B8-D08</v>
@@ -36351,7 +36351,7 @@
         <v>175</v>
       </c>
       <c r="B181" t="str">
-        <v>HV-P230</v>
+        <v>HV-P233</v>
       </c>
       <c r="C181" t="str">
         <v>B8-D09</v>
@@ -36434,7 +36434,7 @@
         <v>176</v>
       </c>
       <c r="B182" t="str">
-        <v>HV-P231</v>
+        <v>HV-P234</v>
       </c>
       <c r="C182" t="str">
         <v>B8-D10</v>
@@ -36517,7 +36517,7 @@
         <v>177</v>
       </c>
       <c r="B183" t="str">
-        <v>HV-P232</v>
+        <v>HV-P235</v>
       </c>
       <c r="C183" t="str">
         <v>B8-D11</v>
@@ -36600,7 +36600,7 @@
         <v>178</v>
       </c>
       <c r="B184" t="str">
-        <v>HV-P233</v>
+        <v>HV-P236</v>
       </c>
       <c r="C184" t="str">
         <v>B8-D12</v>
@@ -36683,7 +36683,7 @@
         <v>179</v>
       </c>
       <c r="B185" t="str">
-        <v>HV-P234</v>
+        <v>HV-P237</v>
       </c>
       <c r="C185" t="str">
         <v>B8-D13</v>
@@ -36766,7 +36766,7 @@
         <v>180</v>
       </c>
       <c r="B186" t="str">
-        <v>HV-P235</v>
+        <v>HV-P238</v>
       </c>
       <c r="C186" t="str">
         <v>B8-D14</v>
@@ -36849,7 +36849,7 @@
         <v>181</v>
       </c>
       <c r="B187" t="str">
-        <v>HV-P236</v>
+        <v>HV-P239</v>
       </c>
       <c r="C187" t="str">
         <v>B8-D15</v>
@@ -36932,7 +36932,7 @@
         <v>182</v>
       </c>
       <c r="B188" t="str">
-        <v>HV-P237</v>
+        <v>HV-P240</v>
       </c>
       <c r="C188" t="str">
         <v>B8-D16</v>
@@ -37015,7 +37015,7 @@
         <v>183</v>
       </c>
       <c r="B189" t="str">
-        <v>HV-P238</v>
+        <v>HV-P241</v>
       </c>
       <c r="C189" t="str">
         <v>B8-D17</v>
@@ -37098,7 +37098,7 @@
         <v>184</v>
       </c>
       <c r="B190" t="str">
-        <v>HV-P239</v>
+        <v>HV-P242</v>
       </c>
       <c r="C190" t="str">
         <v>B8-D18</v>
@@ -37181,7 +37181,7 @@
         <v>185</v>
       </c>
       <c r="B191" t="str">
-        <v>HV-P240</v>
+        <v>HV-P243</v>
       </c>
       <c r="C191" t="str">
         <v>B8-D19</v>
@@ -37264,7 +37264,7 @@
         <v>186</v>
       </c>
       <c r="B192" t="str">
-        <v>HV-P241</v>
+        <v>HV-P244</v>
       </c>
       <c r="C192" t="str">
         <v>B8-D20</v>
@@ -37347,7 +37347,7 @@
         <v>187</v>
       </c>
       <c r="B193" t="str">
-        <v>HV-P242</v>
+        <v>HV-P245</v>
       </c>
       <c r="C193" t="str">
         <v>B8-D21</v>
@@ -37430,7 +37430,7 @@
         <v>188</v>
       </c>
       <c r="B194" t="str">
-        <v>HV-P243</v>
+        <v>HV-P246</v>
       </c>
       <c r="C194" t="str">
         <v>B8-D22</v>
@@ -37513,7 +37513,7 @@
         <v>189</v>
       </c>
       <c r="B195" t="str">
-        <v>HV-P244</v>
+        <v>HV-P247</v>
       </c>
       <c r="C195" t="str">
         <v>B8-D23</v>
@@ -37596,7 +37596,7 @@
         <v>190</v>
       </c>
       <c r="B196" t="str">
-        <v>HV-P245</v>
+        <v>HV-P248</v>
       </c>
       <c r="C196" t="str">
         <v>B8-D24</v>
@@ -37679,7 +37679,7 @@
         <v>191</v>
       </c>
       <c r="B197" t="str">
-        <v>HV-P246</v>
+        <v>HV-P249</v>
       </c>
       <c r="C197" t="str">
         <v>B8-D25</v>
@@ -37762,7 +37762,7 @@
         <v>192</v>
       </c>
       <c r="B198" t="str">
-        <v>HV-P247</v>
+        <v>HV-P250</v>
       </c>
       <c r="C198" t="str">
         <v>B8-D26</v>
@@ -37845,7 +37845,7 @@
         <v>193</v>
       </c>
       <c r="B199" t="str">
-        <v>HV-P248</v>
+        <v>HV-P251</v>
       </c>
       <c r="C199" t="str">
         <v>B8-D27</v>
@@ -37928,7 +37928,7 @@
         <v>194</v>
       </c>
       <c r="B200" t="str">
-        <v>HV-P249</v>
+        <v>HV-P252</v>
       </c>
       <c r="C200" t="str">
         <v>B8-D28</v>
@@ -38011,7 +38011,7 @@
         <v>195</v>
       </c>
       <c r="B201" t="str">
-        <v>HV-P254</v>
+        <v>HV-P257</v>
       </c>
       <c r="C201" t="str">
         <v>B8-D33</v>
@@ -38094,7 +38094,7 @@
         <v>196</v>
       </c>
       <c r="B202" t="str">
-        <v>HV-P255</v>
+        <v>HV-P258</v>
       </c>
       <c r="C202" t="str">
         <v>B8-D34</v>
@@ -38177,7 +38177,7 @@
         <v>197</v>
       </c>
       <c r="B203" t="str">
-        <v>HV-P256</v>
+        <v>HV-P259</v>
       </c>
       <c r="C203" t="str">
         <v>B8-D35</v>
@@ -38260,7 +38260,7 @@
         <v>198</v>
       </c>
       <c r="B204" t="str">
-        <v>HV-P257</v>
+        <v>HV-P260</v>
       </c>
       <c r="C204" t="str">
         <v>B8-D36</v>
@@ -38343,7 +38343,7 @@
         <v>199</v>
       </c>
       <c r="B205" t="str">
-        <v>HV-P258</v>
+        <v>HV-P261</v>
       </c>
       <c r="C205" t="str">
         <v>B8-D37</v>
@@ -38426,7 +38426,7 @@
         <v>200</v>
       </c>
       <c r="B206" t="str">
-        <v>HV-P259</v>
+        <v>HV-P262</v>
       </c>
       <c r="C206" t="str">
         <v>B8-D38</v>
@@ -38509,7 +38509,7 @@
         <v>201</v>
       </c>
       <c r="B207" t="str">
-        <v>HV-P260</v>
+        <v>HV-P263</v>
       </c>
       <c r="C207" t="str">
         <v>B8-D39</v>
@@ -38592,7 +38592,7 @@
         <v>202</v>
       </c>
       <c r="B208" t="str">
-        <v>HV-P261</v>
+        <v>HV-P264</v>
       </c>
       <c r="C208" t="str">
         <v>B8-D40</v>
@@ -38675,7 +38675,7 @@
         <v>203</v>
       </c>
       <c r="B209" t="str">
-        <v>HV-P262</v>
+        <v>HV-P265</v>
       </c>
       <c r="C209" t="str">
         <v>B8-D41</v>
@@ -38758,7 +38758,7 @@
         <v>204</v>
       </c>
       <c r="B210" t="str">
-        <v>HV-P263</v>
+        <v>HV-P266</v>
       </c>
       <c r="C210" t="str">
         <v>B8-D42</v>
@@ -38841,7 +38841,7 @@
         <v>205</v>
       </c>
       <c r="B211" t="str">
-        <v>HV-P264</v>
+        <v>HV-P267</v>
       </c>
       <c r="C211" t="str">
         <v>B8-D43</v>
@@ -38924,7 +38924,7 @@
         <v>206</v>
       </c>
       <c r="B212" t="str">
-        <v>HV-P265</v>
+        <v>HV-P268</v>
       </c>
       <c r="C212" t="str">
         <v>B8-D44</v>
@@ -39007,7 +39007,7 @@
         <v>207</v>
       </c>
       <c r="B213" t="str">
-        <v>HV-P266</v>
+        <v>HV-P269</v>
       </c>
       <c r="C213" t="str">
         <v>B8-D45</v>
@@ -39090,7 +39090,7 @@
         <v>208</v>
       </c>
       <c r="B214" t="str">
-        <v>HV-P267</v>
+        <v>HV-P270</v>
       </c>
       <c r="C214" t="str">
         <v>B8-D46</v>
@@ -39173,7 +39173,7 @@
         <v>209</v>
       </c>
       <c r="B215" t="str">
-        <v>HV-P268</v>
+        <v>HV-P271</v>
       </c>
       <c r="C215" t="str">
         <v>B8-D47</v>
@@ -39256,7 +39256,7 @@
         <v>210</v>
       </c>
       <c r="B216" t="str">
-        <v>HV-P270</v>
+        <v>HV-P273</v>
       </c>
       <c r="C216" t="str">
         <v>B8-D49</v>
@@ -39339,7 +39339,7 @@
         <v>211</v>
       </c>
       <c r="B217" t="str">
-        <v>HV-P271</v>
+        <v>HV-P274</v>
       </c>
       <c r="C217" t="str">
         <v>B8-D50</v>
@@ -39422,7 +39422,7 @@
         <v>212</v>
       </c>
       <c r="B218" t="str">
-        <v>HV-P272</v>
+        <v>HV-P275</v>
       </c>
       <c r="C218" t="str">
         <v>B8-D51</v>
@@ -39505,7 +39505,7 @@
         <v>213</v>
       </c>
       <c r="B219" t="str">
-        <v>HV-P273</v>
+        <v>HV-P276</v>
       </c>
       <c r="C219" t="str">
         <v>B9-D01</v>
@@ -39588,7 +39588,7 @@
         <v>214</v>
       </c>
       <c r="B220" t="str">
-        <v>HV-P274</v>
+        <v>HV-P277</v>
       </c>
       <c r="C220" t="str">
         <v>B9-D02</v>
@@ -39671,7 +39671,7 @@
         <v>215</v>
       </c>
       <c r="B221" t="str">
-        <v>HV-P275</v>
+        <v>HV-P278</v>
       </c>
       <c r="C221" t="str">
         <v>B9-D03</v>
@@ -39754,7 +39754,7 @@
         <v>216</v>
       </c>
       <c r="B222" t="str">
-        <v>HV-P276</v>
+        <v>HV-P279</v>
       </c>
       <c r="C222" t="str">
         <v>B9-D04</v>
@@ -39837,7 +39837,7 @@
         <v>217</v>
       </c>
       <c r="B223" t="str">
-        <v>HV-P277</v>
+        <v>HV-P280</v>
       </c>
       <c r="C223" t="str">
         <v>B9-D05</v>
@@ -39920,7 +39920,7 @@
         <v>218</v>
       </c>
       <c r="B224" t="str">
-        <v>HV-P278</v>
+        <v>HV-P281</v>
       </c>
       <c r="C224" t="str">
         <v>B9-D06</v>
@@ -40003,7 +40003,7 @@
         <v>219</v>
       </c>
       <c r="B225" t="str">
-        <v>HV-P279</v>
+        <v>HV-P282</v>
       </c>
       <c r="C225" t="str">
         <v>B9-D07</v>
@@ -40086,7 +40086,7 @@
         <v>220</v>
       </c>
       <c r="B226" t="str">
-        <v>HV-P280</v>
+        <v>HV-P283</v>
       </c>
       <c r="C226" t="str">
         <v>B9-D08</v>
@@ -40169,7 +40169,7 @@
         <v>221</v>
       </c>
       <c r="B227" t="str">
-        <v>HV-P281</v>
+        <v>HV-P284</v>
       </c>
       <c r="C227" t="str">
         <v>B9-D09</v>
@@ -40252,7 +40252,7 @@
         <v>222</v>
       </c>
       <c r="B228" t="str">
-        <v>HV-P282</v>
+        <v>HV-P285</v>
       </c>
       <c r="C228" t="str">
         <v>B9-D10</v>
@@ -40335,7 +40335,7 @@
         <v>223</v>
       </c>
       <c r="B229" t="str">
-        <v>HV-P283</v>
+        <v>HV-P286</v>
       </c>
       <c r="C229" t="str">
         <v>B9-D11</v>
@@ -40418,7 +40418,7 @@
         <v>224</v>
       </c>
       <c r="B230" t="str">
-        <v>HV-P284</v>
+        <v>HV-P287</v>
       </c>
       <c r="C230" t="str">
         <v>B9-D12</v>
@@ -40501,7 +40501,7 @@
         <v>225</v>
       </c>
       <c r="B231" t="str">
-        <v>HV-P285</v>
+        <v>HV-P288</v>
       </c>
       <c r="C231" t="str">
         <v>B9-D13</v>
@@ -40584,7 +40584,7 @@
         <v>226</v>
       </c>
       <c r="B232" t="str">
-        <v>HV-P286</v>
+        <v>HV-P289</v>
       </c>
       <c r="C232" t="str">
         <v>B9-D14</v>
@@ -40667,7 +40667,7 @@
         <v>227</v>
       </c>
       <c r="B233" t="str">
-        <v>HV-P287</v>
+        <v>HV-P290</v>
       </c>
       <c r="C233" t="str">
         <v>B9-D15</v>
@@ -40750,7 +40750,7 @@
         <v>228</v>
       </c>
       <c r="B234" t="str">
-        <v>HV-P289</v>
+        <v>HV-P292</v>
       </c>
       <c r="C234" t="str">
         <v>B9-D17</v>
@@ -40833,7 +40833,7 @@
         <v>229</v>
       </c>
       <c r="B235" t="str">
-        <v>HV-P290</v>
+        <v>HV-P293</v>
       </c>
       <c r="C235" t="str">
         <v>B9-D18</v>
@@ -40916,7 +40916,7 @@
         <v>230</v>
       </c>
       <c r="B236" t="str">
-        <v>HV-P291</v>
+        <v>HV-P294</v>
       </c>
       <c r="C236" t="str">
         <v>B9-D19</v>
@@ -40999,7 +40999,7 @@
         <v>231</v>
       </c>
       <c r="B237" t="str">
-        <v>HV-P292</v>
+        <v>HV-P295</v>
       </c>
       <c r="C237" t="str">
         <v>B9-D20</v>

--- a/docs/mat-bang-neo-9-be/bang_thong_ke_neo_9_be.xlsx
+++ b/docs/mat-bang-neo-9-be/bang_thong_ke_neo_9_be.xlsx
@@ -3184,13 +3184,13 @@
         <v>BÈ 3</v>
       </c>
       <c r="D49">
-        <v>-41.3</v>
+        <v>-35.8</v>
       </c>
       <c r="E49">
-        <v>-149.57</v>
+        <v>-179.26</v>
       </c>
       <c r="F49">
-        <v>384.08</v>
+        <v>385.08</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -7462,13 +7462,13 @@
         <v>BÈ 5A</v>
       </c>
       <c r="D118">
-        <v>419.48</v>
+        <v>423.01</v>
       </c>
       <c r="E118">
-        <v>-154.12</v>
+        <v>-168.16</v>
       </c>
       <c r="F118">
-        <v>384.2</v>
+        <v>388.57</v>
       </c>
       <c r="G118">
         <v>1</v>
@@ -7524,13 +7524,13 @@
         <v>BÈ 5A</v>
       </c>
       <c r="D119">
-        <v>420.28</v>
+        <v>418.19</v>
       </c>
       <c r="E119">
-        <v>-149.28</v>
+        <v>-162.96</v>
       </c>
       <c r="F119">
-        <v>384.75</v>
+        <v>384</v>
       </c>
       <c r="G119">
         <v>1</v>
@@ -10748,13 +10748,13 @@
         <v>BÈ 7</v>
       </c>
       <c r="D171">
-        <v>76.46</v>
+        <v>81.73</v>
       </c>
       <c r="E171">
-        <v>-76.01</v>
+        <v>-97.29</v>
       </c>
       <c r="F171">
-        <v>384.07</v>
+        <v>384.1</v>
       </c>
       <c r="G171">
         <v>1</v>
@@ -12484,13 +12484,13 @@
         <v>BÈ 8</v>
       </c>
       <c r="D199">
-        <v>41.03</v>
+        <v>47.33</v>
       </c>
       <c r="E199">
-        <v>92.56</v>
+        <v>71.85</v>
       </c>
       <c r="F199">
-        <v>384.03</v>
+        <v>384.01</v>
       </c>
       <c r="G199">
         <v>1</v>
@@ -15048,19 +15048,19 @@
         <v>DÙNG CHUNG</v>
       </c>
       <c r="E7">
-        <v>-139.37</v>
+        <v>-138.58</v>
       </c>
       <c r="F7">
-        <v>30.03</v>
+        <v>31.21</v>
       </c>
       <c r="G7">
         <v>378.3</v>
       </c>
       <c r="H7">
-        <v>11.07</v>
+        <v>11.3</v>
       </c>
       <c r="I7">
-        <v>143.4</v>
+        <v>136.6</v>
       </c>
       <c r="J7">
         <v>2.5</v>
@@ -15090,10 +15090,10 @@
         <v>0.47</v>
       </c>
       <c r="S7">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="T7">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="U7">
         <v>0</v>
@@ -15196,19 +15196,19 @@
         <v>DÙNG CHUNG</v>
       </c>
       <c r="E9">
-        <v>-48.11</v>
+        <v>-48.54</v>
       </c>
       <c r="F9">
-        <v>-33.37</v>
+        <v>-35.03</v>
       </c>
       <c r="G9">
         <v>378.3</v>
       </c>
       <c r="H9">
-        <v>8.91</v>
+        <v>9.01</v>
       </c>
       <c r="I9">
-        <v>102.6</v>
+        <v>113.6</v>
       </c>
       <c r="J9">
         <v>2.5</v>
@@ -15235,16 +15235,16 @@
         <v>38.6</v>
       </c>
       <c r="R9">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="S9">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="T9">
-        <v>0.69</v>
+        <v>0.67</v>
       </c>
       <c r="U9">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="V9">
         <v>0.15</v>
@@ -15270,19 +15270,19 @@
         <v>DÙNG CHUNG</v>
       </c>
       <c r="E10">
-        <v>-25.86</v>
+        <v>-28.46</v>
       </c>
       <c r="F10">
-        <v>-15.46</v>
+        <v>-18.93</v>
       </c>
       <c r="G10">
         <v>378.3</v>
       </c>
       <c r="H10">
-        <v>13.98</v>
+        <v>14.23</v>
       </c>
       <c r="I10">
-        <v>121.3</v>
+        <v>138.9</v>
       </c>
       <c r="J10">
         <v>2.5</v>
@@ -15309,16 +15309,16 @@
         <v>38.6</v>
       </c>
       <c r="R10">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="S10">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="T10">
-        <v>0.56</v>
+        <v>0.51</v>
       </c>
       <c r="U10">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
       <c r="V10">
         <v>0.15</v>
@@ -15344,19 +15344,19 @@
         <v>DÙNG CHUNG</v>
       </c>
       <c r="E11">
-        <v>18.01</v>
+        <v>16.6</v>
       </c>
       <c r="F11">
-        <v>-122.77</v>
+        <v>-124.06</v>
       </c>
       <c r="G11">
         <v>378.3</v>
       </c>
       <c r="H11">
-        <v>9.54</v>
+        <v>9.35</v>
       </c>
       <c r="I11">
-        <v>126.5</v>
+        <v>138</v>
       </c>
       <c r="J11">
         <v>3.25</v>
@@ -15383,16 +15383,16 @@
         <v>73.7</v>
       </c>
       <c r="R11">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="S11">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="T11">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="U11">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="V11">
         <v>0.15</v>
@@ -15418,34 +15418,34 @@
         <v>DÙNG CHUNG</v>
       </c>
       <c r="E12">
-        <v>49.15</v>
+        <v>42.39</v>
       </c>
       <c r="F12">
-        <v>-116.18</v>
+        <v>-119.37</v>
       </c>
       <c r="G12">
         <v>378.3</v>
       </c>
       <c r="H12">
-        <v>15.18</v>
+        <v>15.33</v>
       </c>
       <c r="I12">
-        <v>116.8</v>
+        <v>139.5</v>
       </c>
       <c r="J12">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="K12">
         <v>0.4</v>
       </c>
       <c r="L12">
-        <v>3.01</v>
+        <v>2.48</v>
       </c>
       <c r="M12">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="N12">
-        <v>7.7</v>
+        <v>6.4</v>
       </c>
       <c r="O12">
         <v>4</v>
@@ -15457,16 +15457,16 @@
         <v>73.7</v>
       </c>
       <c r="R12">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="S12">
-        <v>0.69</v>
+        <v>0.75</v>
       </c>
       <c r="T12">
         <v>0.91</v>
       </c>
       <c r="U12">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="V12">
         <v>0.15</v>
@@ -15492,34 +15492,34 @@
         <v>DÙNG CHUNG</v>
       </c>
       <c r="E13">
-        <v>33.69</v>
+        <v>29.5</v>
       </c>
       <c r="F13">
-        <v>-119.71</v>
+        <v>-121.71</v>
       </c>
       <c r="G13">
         <v>378.3</v>
       </c>
       <c r="H13">
-        <v>11.97</v>
+        <v>12.34</v>
       </c>
       <c r="I13">
-        <v>120.7</v>
+        <v>138.9</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="K13">
         <v>0.4</v>
       </c>
       <c r="L13">
-        <v>3.58</v>
+        <v>3.01</v>
       </c>
       <c r="M13">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="N13">
-        <v>9.2</v>
+        <v>7.7</v>
       </c>
       <c r="O13">
         <v>4</v>
@@ -15531,16 +15531,16 @@
         <v>73.7</v>
       </c>
       <c r="R13">
-        <v>0.69</v>
+        <v>0.78</v>
       </c>
       <c r="S13">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="T13">
-        <v>0.91</v>
+        <v>0.94</v>
       </c>
       <c r="U13">
-        <v>0.74</v>
+        <v>0.92</v>
       </c>
       <c r="V13">
         <v>0.15</v>
@@ -15566,34 +15566,34 @@
         <v>DÙNG CHUNG</v>
       </c>
       <c r="E14">
-        <v>0.59</v>
+        <v>5.97</v>
       </c>
       <c r="F14">
-        <v>-131.46</v>
+        <v>-128.68</v>
       </c>
       <c r="G14">
         <v>378.3</v>
       </c>
       <c r="H14">
-        <v>9.76</v>
+        <v>9.59</v>
       </c>
       <c r="I14">
-        <v>172.3</v>
+        <v>135.9</v>
       </c>
       <c r="J14">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K14">
         <v>0.4</v>
       </c>
       <c r="L14">
-        <v>4.21</v>
+        <v>3.58</v>
       </c>
       <c r="M14">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="N14">
-        <v>10.8</v>
+        <v>9.2</v>
       </c>
       <c r="O14">
         <v>4</v>
@@ -15605,16 +15605,16 @@
         <v>73.7</v>
       </c>
       <c r="R14">
-        <v>0.66</v>
+        <v>0.84</v>
       </c>
       <c r="S14">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="T14">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="U14">
-        <v>0.71</v>
+        <v>0.96</v>
       </c>
       <c r="V14">
         <v>0.15</v>
@@ -16380,19 +16380,19 @@
         <v>DÙNG CHUNG</v>
       </c>
       <c r="E25">
-        <v>172.09</v>
+        <v>170.95</v>
       </c>
       <c r="F25">
-        <v>-80.6</v>
+        <v>-78.93</v>
       </c>
       <c r="G25">
         <v>378.3</v>
       </c>
       <c r="H25">
-        <v>12.97</v>
+        <v>14.34</v>
       </c>
       <c r="I25">
-        <v>16.4</v>
+        <v>10.2</v>
       </c>
       <c r="J25">
         <v>2.75</v>
@@ -16419,16 +16419,16 @@
         <v>73.7</v>
       </c>
       <c r="R25">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="S25">
         <v>0.67</v>
       </c>
       <c r="T25">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="U25">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="V25">
         <v>0.15</v>
@@ -16454,19 +16454,19 @@
         <v>DÙNG CHUNG</v>
       </c>
       <c r="E26">
-        <v>157.75</v>
+        <v>156.82</v>
       </c>
       <c r="F26">
-        <v>-78.99</v>
+        <v>-78.93</v>
       </c>
       <c r="G26">
         <v>378.3</v>
       </c>
       <c r="H26">
-        <v>14.29</v>
+        <v>14.36</v>
       </c>
       <c r="I26">
-        <v>14.3</v>
+        <v>10.6</v>
       </c>
       <c r="J26">
         <v>2.75</v>
@@ -16499,7 +16499,7 @@
         <v>0.67</v>
       </c>
       <c r="T26">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="U26">
         <v>0.75</v>
@@ -16528,19 +16528,19 @@
         <v>DÙNG CHUNG</v>
       </c>
       <c r="E27">
-        <v>143.31</v>
+        <v>142.07</v>
       </c>
       <c r="F27">
-        <v>-78.94</v>
+        <v>-78.93</v>
       </c>
       <c r="G27">
         <v>378.3</v>
       </c>
       <c r="H27">
-        <v>14.18</v>
+        <v>14.31</v>
       </c>
       <c r="I27">
-        <v>14.5</v>
+        <v>9.7</v>
       </c>
       <c r="J27">
         <v>2.75</v>
@@ -16570,13 +16570,13 @@
         <v>0.73</v>
       </c>
       <c r="S27">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="T27">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="U27">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="V27">
         <v>0.15</v>
@@ -16602,19 +16602,19 @@
         <v>DÙNG CHUNG</v>
       </c>
       <c r="E28">
-        <v>128.93</v>
+        <v>127.95</v>
       </c>
       <c r="F28">
-        <v>-79.36</v>
+        <v>-78.93</v>
       </c>
       <c r="G28">
         <v>378.3</v>
       </c>
       <c r="H28">
-        <v>14.12</v>
+        <v>14.34</v>
       </c>
       <c r="I28">
-        <v>14.4</v>
+        <v>10.2</v>
       </c>
       <c r="J28">
         <v>2.75</v>
@@ -16647,10 +16647,10 @@
         <v>0.67</v>
       </c>
       <c r="T28">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="U28">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="V28">
         <v>0.15</v>
@@ -16676,19 +16676,19 @@
         <v>DÙNG CHUNG</v>
       </c>
       <c r="E29">
-        <v>114.44</v>
+        <v>113.2</v>
       </c>
       <c r="F29">
-        <v>-78.94</v>
+        <v>-78.93</v>
       </c>
       <c r="G29">
         <v>378.3</v>
       </c>
       <c r="H29">
-        <v>14.17</v>
+        <v>14.29</v>
       </c>
       <c r="I29">
-        <v>14</v>
+        <v>9.2</v>
       </c>
       <c r="J29">
         <v>2.75</v>
@@ -16715,16 +16715,16 @@
         <v>73.7</v>
       </c>
       <c r="R29">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="S29">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="T29">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="U29">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="V29">
         <v>0.15</v>
@@ -16750,34 +16750,34 @@
         <v>DÙNG CHUNG</v>
       </c>
       <c r="E30">
-        <v>371.71</v>
+        <v>369.3</v>
       </c>
       <c r="F30">
-        <v>-73.49</v>
+        <v>-73.82</v>
       </c>
       <c r="G30">
         <v>378.3</v>
       </c>
       <c r="H30">
-        <v>20.76</v>
+        <v>21.3</v>
       </c>
       <c r="I30">
-        <v>14.4</v>
+        <v>8.3</v>
       </c>
       <c r="J30">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="K30">
         <v>0.4</v>
       </c>
       <c r="L30">
-        <v>2.48</v>
+        <v>3.01</v>
       </c>
       <c r="M30">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="N30">
-        <v>6.4</v>
+        <v>7.7</v>
       </c>
       <c r="O30">
         <v>4</v>
@@ -16789,16 +16789,16 @@
         <v>87.3</v>
       </c>
       <c r="R30">
-        <v>0.61</v>
+        <v>0.56</v>
       </c>
       <c r="S30">
-        <v>0.92</v>
+        <v>0.81</v>
       </c>
       <c r="T30">
-        <v>0.94</v>
+        <v>0.84</v>
       </c>
       <c r="U30">
-        <v>0.98</v>
+        <v>0.66</v>
       </c>
       <c r="V30">
         <v>0.15</v>
@@ -16898,19 +16898,19 @@
         <v>DÙNG CHUNG</v>
       </c>
       <c r="E32">
-        <v>337.83</v>
+        <v>346.24</v>
       </c>
       <c r="F32">
-        <v>-69.35</v>
+        <v>-75.68</v>
       </c>
       <c r="G32">
         <v>378.3</v>
       </c>
       <c r="H32">
-        <v>22.08</v>
+        <v>21.45</v>
       </c>
       <c r="I32">
-        <v>2.5</v>
+        <v>26.3</v>
       </c>
       <c r="J32">
         <v>2.75</v>
@@ -16937,16 +16937,16 @@
         <v>87.3</v>
       </c>
       <c r="R32">
-        <v>0.5</v>
+        <v>0.56</v>
       </c>
       <c r="S32">
+        <v>0.81</v>
+      </c>
+      <c r="T32">
         <v>0.83</v>
       </c>
-      <c r="T32">
-        <v>0.87</v>
-      </c>
       <c r="U32">
-        <v>0.74</v>
+        <v>0.65</v>
       </c>
       <c r="V32">
         <v>0.15</v>
@@ -16972,19 +16972,19 @@
         <v>DÙNG CHUNG</v>
       </c>
       <c r="E33">
-        <v>111.96</v>
+        <v>110.63</v>
       </c>
       <c r="F33">
-        <v>89.82</v>
+        <v>90.49</v>
       </c>
       <c r="G33">
         <v>378.3</v>
       </c>
       <c r="H33">
-        <v>10.67</v>
+        <v>11.52</v>
       </c>
       <c r="I33">
-        <v>355.2</v>
+        <v>348.9</v>
       </c>
       <c r="J33">
         <v>2.5</v>
@@ -17017,10 +17017,10 @@
         <v>0.59</v>
       </c>
       <c r="T33">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="U33">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="V33">
         <v>0.15</v>
@@ -17049,16 +17049,16 @@
         <v>130.63</v>
       </c>
       <c r="F34">
-        <v>93.62</v>
+        <v>90.49</v>
       </c>
       <c r="G34">
         <v>378.3</v>
       </c>
       <c r="H34">
-        <v>11.6</v>
+        <v>13.97</v>
       </c>
       <c r="I34">
-        <v>330.3</v>
+        <v>324</v>
       </c>
       <c r="J34">
         <v>2.5</v>
@@ -17085,16 +17085,16 @@
         <v>59.1</v>
       </c>
       <c r="R34">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="S34">
         <v>0.59</v>
       </c>
       <c r="T34">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="U34">
-        <v>0.74</v>
+        <v>0.65</v>
       </c>
       <c r="V34">
         <v>0.15</v>
@@ -17123,16 +17123,16 @@
         <v>83.63</v>
       </c>
       <c r="F35">
-        <v>87.37</v>
+        <v>90.49</v>
       </c>
       <c r="G35">
         <v>378.3</v>
       </c>
       <c r="H35">
-        <v>8.79</v>
+        <v>11.75</v>
       </c>
       <c r="I35">
-        <v>338.5</v>
+        <v>344.1</v>
       </c>
       <c r="J35">
         <v>2.5</v>
@@ -17165,10 +17165,10 @@
         <v>0.59</v>
       </c>
       <c r="T35">
-        <v>0.94</v>
+        <v>0.89</v>
       </c>
       <c r="U35">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="V35">
         <v>0.15</v>
@@ -17268,19 +17268,19 @@
         <v>DÙNG CHUNG</v>
       </c>
       <c r="E37">
-        <v>115.24</v>
+        <v>121.79</v>
       </c>
       <c r="F37">
-        <v>293.32</v>
+        <v>292.95</v>
       </c>
       <c r="G37">
         <v>378.3</v>
       </c>
       <c r="H37">
-        <v>12.14</v>
+        <v>11.49</v>
       </c>
       <c r="I37">
-        <v>341.8</v>
+        <v>13.8</v>
       </c>
       <c r="J37">
         <v>2.5</v>
@@ -17307,16 +17307,16 @@
         <v>59.1</v>
       </c>
       <c r="R37">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="S37">
-        <v>0.87</v>
+        <v>0.59</v>
       </c>
       <c r="T37">
-        <v>0.94</v>
+        <v>0.86</v>
       </c>
       <c r="U37">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="V37">
         <v>0.15</v>
@@ -17376,7 +17376,7 @@
         <v>Tổng bê tông đế</v>
       </c>
       <c r="B43">
-        <v>93.4</v>
+        <v>92.2</v>
       </c>
       <c r="C43" t="str">
         <v>m³</v>
@@ -17387,7 +17387,7 @@
         <v>Tổng thép bản đế (ước tính)</v>
       </c>
       <c r="B44">
-        <v>4.42</v>
+        <v>4.36</v>
       </c>
       <c r="C44" t="str">
         <v>tấn</v>
@@ -17561,19 +17561,19 @@
         <v>Ø12 a200</v>
       </c>
       <c r="F4">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="G4">
-        <v>28.9</v>
+        <v>29.7</v>
       </c>
       <c r="H4">
         <v>30.1</v>
       </c>
       <c r="I4">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="J4">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="K4">
         <v>0.33</v>
@@ -17614,16 +17614,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="F5">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>36.8</v>
+        <v>36.5</v>
       </c>
       <c r="H5">
         <v>27.6</v>
       </c>
       <c r="I5">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="J5">
         <v>0.25</v>
@@ -17667,19 +17667,19 @@
         <v>Ø12 a200</v>
       </c>
       <c r="F6">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>35.3</v>
+        <v>36.5</v>
       </c>
       <c r="H6">
         <v>38.4</v>
       </c>
       <c r="I6">
-        <v>22.3</v>
+        <v>23</v>
       </c>
       <c r="J6">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="K6">
         <v>0.42</v>
@@ -17688,7 +17688,7 @@
         <v>0.54</v>
       </c>
       <c r="M6">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="N6">
         <v>0.15</v>
@@ -17720,19 +17720,19 @@
         <v>Ø12 a200</v>
       </c>
       <c r="F7">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="G7">
-        <v>35</v>
+        <v>35.6</v>
       </c>
       <c r="H7">
         <v>73.3</v>
       </c>
       <c r="I7">
-        <v>42.2</v>
+        <v>42.8</v>
       </c>
       <c r="J7">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="K7">
         <v>0.72</v>
@@ -17741,7 +17741,7 @@
         <v>0.92</v>
       </c>
       <c r="M7">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="N7">
         <v>0.15</v>
@@ -17826,28 +17826,28 @@
         <v>Ø12 a200</v>
       </c>
       <c r="F9">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="G9">
-        <v>37.4</v>
+        <v>30.5</v>
       </c>
       <c r="H9">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="I9">
-        <v>27.7</v>
+        <v>23.1</v>
       </c>
       <c r="J9">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="K9">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="L9">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="M9">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="N9">
         <v>0.15</v>
@@ -17985,25 +17985,25 @@
         <v>Ø12 a200</v>
       </c>
       <c r="F12">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="G12">
-        <v>25.1</v>
+        <v>30.3</v>
       </c>
       <c r="H12">
         <v>30.8</v>
       </c>
       <c r="I12">
-        <v>13.1</v>
+        <v>15.6</v>
       </c>
       <c r="J12">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="K12">
         <v>0.34</v>
       </c>
       <c r="L12">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -18328,7 +18328,7 @@
         <v>30.2</v>
       </c>
       <c r="G8">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="H8" t="str">
         <v>B2-D20</v>
@@ -18340,19 +18340,19 @@
         <v>27.8</v>
       </c>
       <c r="K8">
-        <v>11.07</v>
+        <v>11.3</v>
       </c>
       <c r="L8">
-        <v>-139.37</v>
+        <v>-138.58</v>
       </c>
       <c r="M8">
-        <v>30.03</v>
+        <v>31.21</v>
       </c>
       <c r="N8">
         <v>378.3</v>
       </c>
       <c r="O8">
-        <v>378.87</v>
+        <v>378.71</v>
       </c>
       <c r="P8">
         <v>1.7</v>
@@ -18364,10 +18364,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S8">
-        <v>6.4</v>
+        <v>2.1</v>
       </c>
       <c r="T8">
-        <v>30.8</v>
+        <v>31</v>
       </c>
       <c r="U8">
         <v>2.5</v>
@@ -18391,10 +18391,10 @@
         <v>0.47</v>
       </c>
       <c r="AB8">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="AC8">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -18412,7 +18412,7 @@
         <v>ĐẠT</v>
       </c>
       <c r="AI8" t="str">
-        <v>Đế dùng chung hai bè: hai tai neo; Địa hình IFC tại điểm này cao hơn đáy thiết kế 0,6 m: kiểm tra khảo sát / nạo vét trước khi đặt đế</v>
+        <v>Đế dùng chung hai bè: hai tai neo</v>
       </c>
     </row>
     <row r="9">
@@ -18542,7 +18542,7 @@
         <v>27.8</v>
       </c>
       <c r="G10">
-        <v>8.91</v>
+        <v>9.01</v>
       </c>
       <c r="H10" t="str">
         <v>B3-D17</v>
@@ -18554,13 +18554,13 @@
         <v>38.6</v>
       </c>
       <c r="K10">
-        <v>9.44</v>
+        <v>9.02</v>
       </c>
       <c r="L10">
-        <v>-48.11</v>
+        <v>-48.54</v>
       </c>
       <c r="M10">
-        <v>-33.37</v>
+        <v>-35.03</v>
       </c>
       <c r="N10">
         <v>378.3</v>
@@ -18578,10 +18578,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S10">
-        <v>13.3</v>
+        <v>8.5</v>
       </c>
       <c r="T10">
-        <v>40.7</v>
+        <v>41.3</v>
       </c>
       <c r="U10">
         <v>2.5</v>
@@ -18602,16 +18602,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA10">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="AB10">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AC10">
-        <v>0.69</v>
+        <v>0.67</v>
       </c>
       <c r="AD10">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AE10">
         <v>0.15</v>
@@ -18620,7 +18620,7 @@
         <v>0.62</v>
       </c>
       <c r="AG10">
-        <v>0.69</v>
+        <v>0.67</v>
       </c>
       <c r="AH10" t="str">
         <v>ĐẠT</v>
@@ -18649,7 +18649,7 @@
         <v>27.8</v>
       </c>
       <c r="G11">
-        <v>13.98</v>
+        <v>14.23</v>
       </c>
       <c r="H11" t="str">
         <v>B3-D13</v>
@@ -18661,19 +18661,19 @@
         <v>38.6</v>
       </c>
       <c r="K11">
-        <v>15.72</v>
+        <v>14.23</v>
       </c>
       <c r="L11">
-        <v>-25.86</v>
+        <v>-28.46</v>
       </c>
       <c r="M11">
-        <v>-15.46</v>
+        <v>-18.93</v>
       </c>
       <c r="N11">
         <v>378.3</v>
       </c>
       <c r="O11">
-        <v>378.54</v>
+        <v>378.5</v>
       </c>
       <c r="P11">
         <v>1.7</v>
@@ -18685,10 +18685,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S11">
-        <v>19.9</v>
+        <v>9.7</v>
       </c>
       <c r="T11">
-        <v>28.6</v>
+        <v>29.8</v>
       </c>
       <c r="U11">
         <v>2.5</v>
@@ -18709,16 +18709,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA11">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="AB11">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="AC11">
-        <v>0.56</v>
+        <v>0.51</v>
       </c>
       <c r="AD11">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
       <c r="AE11">
         <v>0.15</v>
@@ -18756,7 +18756,7 @@
         <v>38.6</v>
       </c>
       <c r="G12">
-        <v>9.54</v>
+        <v>9.36</v>
       </c>
       <c r="H12" t="str">
         <v>B3A-D23</v>
@@ -18768,13 +18768,13 @@
         <v>73.7</v>
       </c>
       <c r="K12">
-        <v>9.56</v>
+        <v>9.35</v>
       </c>
       <c r="L12">
-        <v>18.01</v>
+        <v>16.6</v>
       </c>
       <c r="M12">
-        <v>-122.77</v>
+        <v>-124.06</v>
       </c>
       <c r="N12">
         <v>378.3</v>
@@ -18792,10 +18792,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S12">
-        <v>32.9</v>
+        <v>27.8</v>
       </c>
       <c r="T12">
-        <v>67.3</v>
+        <v>68.2</v>
       </c>
       <c r="U12">
         <v>3.25</v>
@@ -18816,16 +18816,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA12">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="AB12">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="AC12">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="AD12">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="AE12">
         <v>0.15</v>
@@ -18834,7 +18834,7 @@
         <v>0.62</v>
       </c>
       <c r="AG12">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="AH12" t="str">
         <v>ĐẠT</v>
@@ -18863,7 +18863,7 @@
         <v>38.6</v>
       </c>
       <c r="G13">
-        <v>18.74</v>
+        <v>15.33</v>
       </c>
       <c r="H13" t="str">
         <v>B3A-D21</v>
@@ -18875,19 +18875,19 @@
         <v>73.7</v>
       </c>
       <c r="K13">
-        <v>15.18</v>
+        <v>15.33</v>
       </c>
       <c r="L13">
-        <v>49.15</v>
+        <v>42.39</v>
       </c>
       <c r="M13">
-        <v>-116.18</v>
+        <v>-119.37</v>
       </c>
       <c r="N13">
         <v>378.3</v>
       </c>
       <c r="O13">
-        <v>378.89</v>
+        <v>378.5</v>
       </c>
       <c r="P13">
         <v>1.7</v>
@@ -18899,40 +18899,40 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S13">
-        <v>52.1</v>
+        <v>31.7</v>
       </c>
       <c r="T13">
-        <v>45.2</v>
+        <v>47.5</v>
       </c>
       <c r="U13">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V13">
         <v>0.4</v>
       </c>
       <c r="W13">
-        <v>45.4</v>
+        <v>37.5</v>
       </c>
       <c r="X13">
-        <v>3.01</v>
+        <v>2.48</v>
       </c>
       <c r="Y13">
-        <v>7.7</v>
+        <v>6.4</v>
       </c>
       <c r="Z13" t="str">
         <v>Ø12 a200</v>
       </c>
       <c r="AA13">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="AB13">
-        <v>0.69</v>
+        <v>0.75</v>
       </c>
       <c r="AC13">
         <v>0.91</v>
       </c>
       <c r="AD13">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="AE13">
         <v>0.15</v>
@@ -18941,13 +18941,13 @@
         <v>0.62</v>
       </c>
       <c r="AG13">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="AH13" t="str">
         <v>ĐẠT</v>
       </c>
       <c r="AI13" t="str">
-        <v>Đế dùng chung hai bè: hai tai neo; Địa hình IFC tại điểm này cao hơn đáy thiết kế 0,6 m: kiểm tra khảo sát / nạo vét trước khi đặt đế; Đế lớn hơn đế mẫu</v>
+        <v>Đế dùng chung hai bè: hai tai neo</v>
       </c>
     </row>
     <row r="14">
@@ -18970,7 +18970,7 @@
         <v>38.6</v>
       </c>
       <c r="G14">
-        <v>14.3</v>
+        <v>12.34</v>
       </c>
       <c r="H14" t="str">
         <v>B3A-D22</v>
@@ -18982,13 +18982,13 @@
         <v>73.7</v>
       </c>
       <c r="K14">
-        <v>11.97</v>
+        <v>12.34</v>
       </c>
       <c r="L14">
-        <v>33.69</v>
+        <v>29.5</v>
       </c>
       <c r="M14">
-        <v>-119.71</v>
+        <v>-121.71</v>
       </c>
       <c r="N14">
         <v>378.3</v>
@@ -19006,40 +19006,40 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S14">
-        <v>43.1</v>
+        <v>30.3</v>
       </c>
       <c r="T14">
-        <v>55.1</v>
+        <v>56.3</v>
       </c>
       <c r="U14">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="V14">
         <v>0.4</v>
       </c>
       <c r="W14">
-        <v>54</v>
+        <v>45.4</v>
       </c>
       <c r="X14">
-        <v>3.58</v>
+        <v>3.01</v>
       </c>
       <c r="Y14">
-        <v>9.2</v>
+        <v>7.7</v>
       </c>
       <c r="Z14" t="str">
         <v>Ø12 a200</v>
       </c>
       <c r="AA14">
-        <v>0.69</v>
+        <v>0.78</v>
       </c>
       <c r="AB14">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="AC14">
-        <v>0.91</v>
+        <v>0.94</v>
       </c>
       <c r="AD14">
-        <v>0.74</v>
+        <v>0.92</v>
       </c>
       <c r="AE14">
         <v>0.15</v>
@@ -19048,7 +19048,7 @@
         <v>0.62</v>
       </c>
       <c r="AG14">
-        <v>0.91</v>
+        <v>0.94</v>
       </c>
       <c r="AH14" t="str">
         <v>ĐẠT</v>
@@ -19077,7 +19077,7 @@
         <v>38.6</v>
       </c>
       <c r="G15">
-        <v>9.76</v>
+        <v>9.6</v>
       </c>
       <c r="H15" t="str">
         <v>B3A-D24</v>
@@ -19089,13 +19089,13 @@
         <v>73.7</v>
       </c>
       <c r="K15">
-        <v>12.73</v>
+        <v>9.59</v>
       </c>
       <c r="L15">
-        <v>0.59</v>
+        <v>5.97</v>
       </c>
       <c r="M15">
-        <v>-131.46</v>
+        <v>-128.68</v>
       </c>
       <c r="N15">
         <v>378.3</v>
@@ -19113,40 +19113,40 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S15">
-        <v>57.5</v>
+        <v>28.1</v>
       </c>
       <c r="T15">
-        <v>58.9</v>
+        <v>67.1</v>
       </c>
       <c r="U15">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="V15">
         <v>0.4</v>
       </c>
       <c r="W15">
-        <v>63.4</v>
+        <v>54</v>
       </c>
       <c r="X15">
-        <v>4.21</v>
+        <v>3.58</v>
       </c>
       <c r="Y15">
-        <v>10.8</v>
+        <v>9.2</v>
       </c>
       <c r="Z15" t="str">
         <v>Ø12 a200</v>
       </c>
       <c r="AA15">
-        <v>0.66</v>
+        <v>0.84</v>
       </c>
       <c r="AB15">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="AC15">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="AD15">
-        <v>0.71</v>
+        <v>0.96</v>
       </c>
       <c r="AE15">
         <v>0.15</v>
@@ -19155,7 +19155,7 @@
         <v>0.62</v>
       </c>
       <c r="AG15">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="AH15" t="str">
         <v>ĐẠT</v>
@@ -20254,7 +20254,7 @@
         <v>73.7</v>
       </c>
       <c r="G26">
-        <v>12.97</v>
+        <v>14.34</v>
       </c>
       <c r="H26" t="str">
         <v>B7-D23</v>
@@ -20266,13 +20266,13 @@
         <v>45.6</v>
       </c>
       <c r="K26">
-        <v>15.85</v>
+        <v>14.34</v>
       </c>
       <c r="L26">
-        <v>172.09</v>
+        <v>170.95</v>
       </c>
       <c r="M26">
-        <v>-80.6</v>
+        <v>-78.93</v>
       </c>
       <c r="N26">
         <v>378.3</v>
@@ -20290,10 +20290,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S26">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="T26">
-        <v>54.3</v>
+        <v>53.2</v>
       </c>
       <c r="U26">
         <v>2.75</v>
@@ -20314,16 +20314,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA26">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="AB26">
         <v>0.67</v>
       </c>
       <c r="AC26">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="AD26">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="AE26">
         <v>0.15</v>
@@ -20332,7 +20332,7 @@
         <v>0.62</v>
       </c>
       <c r="AG26">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="AH26" t="str">
         <v>ĐẠT</v>
@@ -20361,7 +20361,7 @@
         <v>73.7</v>
       </c>
       <c r="G27">
-        <v>14.5</v>
+        <v>14.36</v>
       </c>
       <c r="H27" t="str">
         <v>B7-D32</v>
@@ -20373,13 +20373,13 @@
         <v>45.6</v>
       </c>
       <c r="K27">
-        <v>14.29</v>
+        <v>14.37</v>
       </c>
       <c r="L27">
-        <v>157.75</v>
+        <v>156.82</v>
       </c>
       <c r="M27">
-        <v>-78.99</v>
+        <v>-78.93</v>
       </c>
       <c r="N27">
         <v>378.3</v>
@@ -20397,10 +20397,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S27">
-        <v>26.2</v>
+        <v>25.1</v>
       </c>
       <c r="T27">
-        <v>53</v>
+        <v>53.1</v>
       </c>
       <c r="U27">
         <v>2.75</v>
@@ -20427,7 +20427,7 @@
         <v>0.67</v>
       </c>
       <c r="AC27">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="AD27">
         <v>0.75</v>
@@ -20439,7 +20439,7 @@
         <v>0.62</v>
       </c>
       <c r="AG27">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="AH27" t="str">
         <v>ĐẠT</v>
@@ -20468,7 +20468,7 @@
         <v>73.7</v>
       </c>
       <c r="G28">
-        <v>14.56</v>
+        <v>14.31</v>
       </c>
       <c r="H28" t="str">
         <v>B7-D19</v>
@@ -20480,13 +20480,13 @@
         <v>45.6</v>
       </c>
       <c r="K28">
-        <v>14.18</v>
+        <v>14.32</v>
       </c>
       <c r="L28">
-        <v>143.31</v>
+        <v>142.07</v>
       </c>
       <c r="M28">
-        <v>-78.94</v>
+        <v>-78.93</v>
       </c>
       <c r="N28">
         <v>378.3</v>
@@ -20504,10 +20504,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S28">
-        <v>26.9</v>
+        <v>25.1</v>
       </c>
       <c r="T28">
-        <v>53</v>
+        <v>53.3</v>
       </c>
       <c r="U28">
         <v>2.75</v>
@@ -20531,13 +20531,13 @@
         <v>0.73</v>
       </c>
       <c r="AB28">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="AC28">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="AD28">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="AE28">
         <v>0.15</v>
@@ -20546,7 +20546,7 @@
         <v>0.62</v>
       </c>
       <c r="AG28">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="AH28" t="str">
         <v>ĐẠT</v>
@@ -20575,7 +20575,7 @@
         <v>73.7</v>
       </c>
       <c r="G29">
-        <v>14.12</v>
+        <v>14.34</v>
       </c>
       <c r="H29" t="str">
         <v>B7-D31</v>
@@ -20587,13 +20587,13 @@
         <v>45.6</v>
       </c>
       <c r="K29">
-        <v>14.63</v>
+        <v>14.34</v>
       </c>
       <c r="L29">
-        <v>128.93</v>
+        <v>127.95</v>
       </c>
       <c r="M29">
-        <v>-79.36</v>
+        <v>-78.93</v>
       </c>
       <c r="N29">
         <v>378.3</v>
@@ -20611,10 +20611,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S29">
-        <v>25.9</v>
+        <v>25.1</v>
       </c>
       <c r="T29">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
       <c r="U29">
         <v>2.75</v>
@@ -20641,10 +20641,10 @@
         <v>0.67</v>
       </c>
       <c r="AC29">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="AD29">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="AE29">
         <v>0.15</v>
@@ -20653,7 +20653,7 @@
         <v>0.62</v>
       </c>
       <c r="AG29">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="AH29" t="str">
         <v>ĐẠT</v>
@@ -20682,7 +20682,7 @@
         <v>73.7</v>
       </c>
       <c r="G30">
-        <v>14.53</v>
+        <v>14.29</v>
       </c>
       <c r="H30" t="str">
         <v>B7-D22</v>
@@ -20694,13 +20694,13 @@
         <v>45.6</v>
       </c>
       <c r="K30">
-        <v>14.17</v>
+        <v>14.3</v>
       </c>
       <c r="L30">
-        <v>114.44</v>
+        <v>113.2</v>
       </c>
       <c r="M30">
-        <v>-78.94</v>
+        <v>-78.93</v>
       </c>
       <c r="N30">
         <v>378.3</v>
@@ -20718,10 +20718,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S30">
-        <v>26.9</v>
+        <v>25.1</v>
       </c>
       <c r="T30">
-        <v>53.1</v>
+        <v>53.3</v>
       </c>
       <c r="U30">
         <v>2.75</v>
@@ -20742,16 +20742,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA30">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="AB30">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="AC30">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="AD30">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="AE30">
         <v>0.15</v>
@@ -20760,7 +20760,7 @@
         <v>0.62</v>
       </c>
       <c r="AG30">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="AH30" t="str">
         <v>ĐẠT</v>
@@ -20789,7 +20789,7 @@
         <v>87.3</v>
       </c>
       <c r="G31">
-        <v>22.11</v>
+        <v>21.31</v>
       </c>
       <c r="H31" t="str">
         <v>B6-D27</v>
@@ -20801,19 +20801,19 @@
         <v>40.8</v>
       </c>
       <c r="K31">
-        <v>20.76</v>
+        <v>21.3</v>
       </c>
       <c r="L31">
-        <v>371.71</v>
+        <v>369.3</v>
       </c>
       <c r="M31">
-        <v>-73.49</v>
+        <v>-73.82</v>
       </c>
       <c r="N31">
         <v>378.3</v>
       </c>
       <c r="O31">
-        <v>381.41</v>
+        <v>381.37</v>
       </c>
       <c r="P31">
         <v>1.7</v>
@@ -20825,40 +20825,40 @@
         <v>B5A-D13 căng, B6-D27 chùng (MN cao)</v>
       </c>
       <c r="S31">
-        <v>78.5</v>
+        <v>78.1</v>
       </c>
       <c r="T31">
-        <v>28.5</v>
+        <v>29.4</v>
       </c>
       <c r="U31">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V31">
         <v>0.4</v>
       </c>
       <c r="W31">
-        <v>37.5</v>
+        <v>45.4</v>
       </c>
       <c r="X31">
-        <v>2.48</v>
+        <v>3.01</v>
       </c>
       <c r="Y31">
-        <v>6.4</v>
+        <v>7.7</v>
       </c>
       <c r="Z31" t="str">
         <v>Ø12 a200</v>
       </c>
       <c r="AA31">
-        <v>0.61</v>
+        <v>0.56</v>
       </c>
       <c r="AB31">
-        <v>0.92</v>
+        <v>0.81</v>
       </c>
       <c r="AC31">
-        <v>0.94</v>
+        <v>0.84</v>
       </c>
       <c r="AD31">
-        <v>0.98</v>
+        <v>0.66</v>
       </c>
       <c r="AE31">
         <v>0.15</v>
@@ -20867,13 +20867,13 @@
         <v>0.62</v>
       </c>
       <c r="AG31">
-        <v>0.98</v>
+        <v>0.84</v>
       </c>
       <c r="AH31" t="str">
         <v>ĐẠT</v>
       </c>
       <c r="AI31" t="str">
-        <v>Đế dùng chung hai bè: hai tai neo; Địa hình IFC tại điểm này cao hơn đáy thiết kế 3,1 m: kiểm tra khảo sát / nạo vét trước khi đặt đế</v>
+        <v>Đế dùng chung hai bè: hai tai neo; Địa hình IFC tại điểm này cao hơn đáy thiết kế 3,1 m: kiểm tra khảo sát / nạo vét trước khi đặt đế; Đế lớn hơn đế mẫu</v>
       </c>
     </row>
     <row r="32">
@@ -21003,7 +21003,7 @@
         <v>87.3</v>
       </c>
       <c r="G33">
-        <v>25.58</v>
+        <v>21.46</v>
       </c>
       <c r="H33" t="str">
         <v>B6-D17</v>
@@ -21015,19 +21015,19 @@
         <v>40.8</v>
       </c>
       <c r="K33">
-        <v>22.08</v>
+        <v>21.45</v>
       </c>
       <c r="L33">
-        <v>337.83</v>
+        <v>346.24</v>
       </c>
       <c r="M33">
-        <v>-69.35</v>
+        <v>-75.68</v>
       </c>
       <c r="N33">
         <v>378.3</v>
       </c>
       <c r="O33">
-        <v>381.18</v>
+        <v>381.05</v>
       </c>
       <c r="P33">
         <v>1.7</v>
@@ -21036,13 +21036,13 @@
         <v>7.7</v>
       </c>
       <c r="R33" t="str">
-        <v>cả hai dây căng (MN cao)</v>
+        <v>B5A-D15 căng, B6-D17 chùng (MN cao)</v>
       </c>
       <c r="S33">
-        <v>67.4</v>
+        <v>78.1</v>
       </c>
       <c r="T33">
-        <v>36.1</v>
+        <v>29.2</v>
       </c>
       <c r="U33">
         <v>2.75</v>
@@ -21063,16 +21063,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA33">
-        <v>0.5</v>
+        <v>0.56</v>
       </c>
       <c r="AB33">
+        <v>0.81</v>
+      </c>
+      <c r="AC33">
         <v>0.83</v>
       </c>
-      <c r="AC33">
-        <v>0.87</v>
-      </c>
       <c r="AD33">
-        <v>0.74</v>
+        <v>0.65</v>
       </c>
       <c r="AE33">
         <v>0.15</v>
@@ -21081,13 +21081,13 @@
         <v>0.62</v>
       </c>
       <c r="AG33">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="AH33" t="str">
         <v>ĐẠT</v>
       </c>
       <c r="AI33" t="str">
-        <v>Đế dùng chung hai bè: hai tai neo; Địa hình IFC tại điểm này cao hơn đáy thiết kế 2,9 m: kiểm tra khảo sát / nạo vét trước khi đặt đế; Đế lớn hơn đế mẫu</v>
+        <v>Đế dùng chung hai bè: hai tai neo; Địa hình IFC tại điểm này cao hơn đáy thiết kế 2,8 m: kiểm tra khảo sát / nạo vét trước khi đặt đế; Đế lớn hơn đế mẫu</v>
       </c>
     </row>
     <row r="34">
@@ -21110,7 +21110,7 @@
         <v>45.6</v>
       </c>
       <c r="G34">
-        <v>10.67</v>
+        <v>11.52</v>
       </c>
       <c r="H34" t="str">
         <v>B8-D31</v>
@@ -21122,13 +21122,13 @@
         <v>59.1</v>
       </c>
       <c r="K34">
-        <v>12.49</v>
+        <v>11.52</v>
       </c>
       <c r="L34">
-        <v>111.96</v>
+        <v>110.63</v>
       </c>
       <c r="M34">
-        <v>89.82</v>
+        <v>90.49</v>
       </c>
       <c r="N34">
         <v>378.3</v>
@@ -21146,10 +21146,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S34">
-        <v>16.2</v>
+        <v>11.5</v>
       </c>
       <c r="T34">
-        <v>54.7</v>
+        <v>55.2</v>
       </c>
       <c r="U34">
         <v>2.5</v>
@@ -21176,10 +21176,10 @@
         <v>0.59</v>
       </c>
       <c r="AC34">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="AD34">
-        <v>0.95</v>
+        <v>0.89</v>
       </c>
       <c r="AE34">
         <v>0.15</v>
@@ -21188,7 +21188,7 @@
         <v>0.62</v>
       </c>
       <c r="AG34">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AH34" t="str">
         <v>ĐẠT</v>
@@ -21217,7 +21217,7 @@
         <v>45.6</v>
       </c>
       <c r="G35">
-        <v>16.61</v>
+        <v>13.97</v>
       </c>
       <c r="H35" t="str">
         <v>B8-D32</v>
@@ -21229,13 +21229,13 @@
         <v>59.1</v>
       </c>
       <c r="K35">
-        <v>11.6</v>
+        <v>13.98</v>
       </c>
       <c r="L35">
         <v>130.63</v>
       </c>
       <c r="M35">
-        <v>93.62</v>
+        <v>90.49</v>
       </c>
       <c r="N35">
         <v>378.3</v>
@@ -21253,10 +21253,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S35">
-        <v>15</v>
+        <v>12.1</v>
       </c>
       <c r="T35">
-        <v>49</v>
+        <v>47.7</v>
       </c>
       <c r="U35">
         <v>2.5</v>
@@ -21277,16 +21277,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA35">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="AB35">
         <v>0.59</v>
       </c>
       <c r="AC35">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="AD35">
-        <v>0.74</v>
+        <v>0.65</v>
       </c>
       <c r="AE35">
         <v>0.15</v>
@@ -21295,7 +21295,7 @@
         <v>0.62</v>
       </c>
       <c r="AG35">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="AH35" t="str">
         <v>ĐẠT</v>
@@ -21324,7 +21324,7 @@
         <v>45.6</v>
       </c>
       <c r="G36">
-        <v>8.79</v>
+        <v>11.75</v>
       </c>
       <c r="H36" t="str">
         <v>B8-D29</v>
@@ -21336,13 +21336,13 @@
         <v>59.1</v>
       </c>
       <c r="K36">
-        <v>14.78</v>
+        <v>11.75</v>
       </c>
       <c r="L36">
         <v>83.63</v>
       </c>
       <c r="M36">
-        <v>87.37</v>
+        <v>90.49</v>
       </c>
       <c r="N36">
         <v>378.3</v>
@@ -21360,10 +21360,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S36">
-        <v>19.1</v>
+        <v>11.6</v>
       </c>
       <c r="T36">
-        <v>54.5</v>
+        <v>54.4</v>
       </c>
       <c r="U36">
         <v>2.5</v>
@@ -21390,10 +21390,10 @@
         <v>0.59</v>
       </c>
       <c r="AC36">
-        <v>0.94</v>
+        <v>0.89</v>
       </c>
       <c r="AD36">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="AE36">
         <v>0.15</v>
@@ -21402,7 +21402,7 @@
         <v>0.62</v>
       </c>
       <c r="AG36">
-        <v>0.98</v>
+        <v>0.89</v>
       </c>
       <c r="AH36" t="str">
         <v>ĐẠT</v>
@@ -21538,7 +21538,7 @@
         <v>59.1</v>
       </c>
       <c r="G38">
-        <v>12.14</v>
+        <v>11.49</v>
       </c>
       <c r="H38" t="str">
         <v>B9-D16</v>
@@ -21550,19 +21550,19 @@
         <v>30.9</v>
       </c>
       <c r="K38">
-        <v>14.24</v>
+        <v>11.49</v>
       </c>
       <c r="L38">
-        <v>115.24</v>
+        <v>121.79</v>
       </c>
       <c r="M38">
-        <v>293.32</v>
+        <v>292.95</v>
       </c>
       <c r="N38">
         <v>378.3</v>
       </c>
       <c r="O38">
-        <v>380.69</v>
+        <v>380.8</v>
       </c>
       <c r="P38">
         <v>1.7</v>
@@ -21574,10 +21574,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S38">
-        <v>43.6</v>
+        <v>24</v>
       </c>
       <c r="T38">
-        <v>43.9</v>
+        <v>47.6</v>
       </c>
       <c r="U38">
         <v>2.5</v>
@@ -21598,16 +21598,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA38">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="AB38">
-        <v>0.87</v>
+        <v>0.59</v>
       </c>
       <c r="AC38">
-        <v>0.94</v>
+        <v>0.86</v>
       </c>
       <c r="AD38">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="AE38">
         <v>0.15</v>
@@ -21616,13 +21616,13 @@
         <v>0.62</v>
       </c>
       <c r="AG38">
-        <v>0.98</v>
+        <v>0.86</v>
       </c>
       <c r="AH38" t="str">
         <v>ĐẠT</v>
       </c>
       <c r="AI38" t="str">
-        <v>Đế dùng chung hai bè: hai tai neo; Địa hình IFC tại điểm này cao hơn đáy thiết kế 2,4 m: kiểm tra khảo sát / nạo vét trước khi đặt đế</v>
+        <v>Đế dùng chung hai bè: hai tai neo; Địa hình IFC tại điểm này cao hơn đáy thiết kế 2,5 m: kiểm tra khảo sát / nạo vét trước khi đặt đế</v>
       </c>
     </row>
     <row r="39">
@@ -21684,7 +21684,7 @@
         <v>Bê tông đế</v>
       </c>
       <c r="B45">
-        <v>93.4</v>
+        <v>92.2</v>
       </c>
       <c r="C45" t="str">
         <v>m³</v>
@@ -21717,7 +21717,7 @@
         <v>Số đế cạnh B = 2,75 m</v>
       </c>
       <c r="B48">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C48" t="str">
         <v>đế</v>
@@ -21739,7 +21739,7 @@
         <v>Số đế cạnh B = 3,25 m</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" t="str">
         <v>đế</v>
@@ -21750,7 +21750,7 @@
         <v>Số đế mà địa hình IFC cao hơn đáy thiết kế trên 0,5 m (cần kiểm tra khảo sát / nạo vét)</v>
       </c>
       <c r="B51">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C51" t="str">
         <v>đế</v>
@@ -25490,19 +25490,19 @@
         <v>Chuyển từ neo đáy</v>
       </c>
       <c r="F50">
-        <v>-41.3</v>
+        <v>-35.8</v>
       </c>
       <c r="G50">
-        <v>-149.57</v>
+        <v>-179.26</v>
       </c>
       <c r="H50">
-        <v>384.08</v>
+        <v>385.08</v>
       </c>
       <c r="I50">
-        <v>37.5</v>
+        <v>58</v>
       </c>
       <c r="J50">
-        <v>232</v>
+        <v>204.5</v>
       </c>
       <c r="K50">
         <v>1</v>
@@ -25538,13 +25538,13 @@
         <v>H-8 Cao độ chốt cáp so với yêu cầu thiết kế cọc</v>
       </c>
       <c r="V50">
-        <v>-5.8</v>
+        <v>-4.8</v>
       </c>
       <c r="W50">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="X50" t="str">
-        <v>CÓ</v>
+        <v>không</v>
       </c>
       <c r="Y50" t="str">
         <v>CÓ</v>
@@ -25553,7 +25553,7 @@
         <v>ĐẠT</v>
       </c>
       <c r="AA50" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
       </c>
     </row>
     <row r="51">
@@ -31217,19 +31217,19 @@
         <v>Chuyển từ neo đáy</v>
       </c>
       <c r="F119">
-        <v>419.48</v>
+        <v>423.01</v>
       </c>
       <c r="G119">
-        <v>-154.12</v>
+        <v>-168.16</v>
       </c>
       <c r="H119">
-        <v>384.2</v>
+        <v>388.57</v>
       </c>
       <c r="I119">
-        <v>49.52</v>
+        <v>58.5</v>
       </c>
       <c r="J119">
-        <v>107.9</v>
+        <v>120</v>
       </c>
       <c r="K119">
         <v>1</v>
@@ -31265,22 +31265,22 @@
         <v>H-8 Cao độ chốt cáp so với yêu cầu thiết kế cọc</v>
       </c>
       <c r="V119">
-        <v>-4.6</v>
+        <v>-8.1</v>
       </c>
       <c r="W119">
-        <v>2.4</v>
+        <v>-2.3</v>
       </c>
       <c r="X119" t="str">
-        <v>CÓ</v>
+        <v>không</v>
       </c>
       <c r="Y119" t="str">
-        <v>CÓ</v>
+        <v>không</v>
       </c>
       <c r="Z119" t="str">
         <v>ĐẠT</v>
       </c>
       <c r="AA119" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ)</v>
       </c>
     </row>
     <row r="120">
@@ -31300,19 +31300,19 @@
         <v>Chuyển từ neo đáy</v>
       </c>
       <c r="F120">
-        <v>420.28</v>
+        <v>418.19</v>
       </c>
       <c r="G120">
-        <v>-149.28</v>
+        <v>-162.96</v>
       </c>
       <c r="H120">
-        <v>384.75</v>
+        <v>384</v>
       </c>
       <c r="I120">
-        <v>35</v>
+        <v>39.5</v>
       </c>
       <c r="J120">
-        <v>107.2</v>
+        <v>127.5</v>
       </c>
       <c r="K120">
         <v>1</v>
@@ -31348,13 +31348,13 @@
         <v>H-8 Cao độ chốt cáp so với yêu cầu thiết kế cọc</v>
       </c>
       <c r="V120">
-        <v>-7.3</v>
+        <v>-5.4</v>
       </c>
       <c r="W120">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="X120" t="str">
-        <v>không</v>
+        <v>CÓ</v>
       </c>
       <c r="Y120" t="str">
         <v>CÓ</v>
@@ -31363,7 +31363,7 @@
         <v>ĐẠT</v>
       </c>
       <c r="AA120" t="str">
-        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
+        <v>Chuyển từ neo đáy sang cọc khoan nhồi (vị trí ven bờ); Mặt đất tại cọc thấp hơn MNDB: thi công mùa nước thấp, có ống vách; Đầu cọc ngập khi hồ ở MNLKT: bản mã, tai neo cần chống gỉ</v>
       </c>
     </row>
     <row r="121">
@@ -35616,19 +35616,19 @@
         <v>Chuyển từ neo đáy</v>
       </c>
       <c r="F172">
-        <v>76.46</v>
+        <v>81.73</v>
       </c>
       <c r="G172">
-        <v>-76.01</v>
+        <v>-97.29</v>
       </c>
       <c r="H172">
-        <v>384.07</v>
+        <v>384.1</v>
       </c>
       <c r="I172">
-        <v>26.5</v>
+        <v>37.5</v>
       </c>
       <c r="J172">
-        <v>245</v>
+        <v>210</v>
       </c>
       <c r="K172">
         <v>1</v>
@@ -35664,10 +35664,10 @@
         <v>H-8 Cao độ chốt cáp so với yêu cầu thiết kế cọc</v>
       </c>
       <c r="V172">
-        <v>-8.2</v>
+        <v>-5.9</v>
       </c>
       <c r="W172">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="X172" t="str">
         <v>CÓ</v>
@@ -37940,19 +37940,19 @@
         <v>Chuyển từ neo đáy</v>
       </c>
       <c r="F200">
-        <v>41.03</v>
+        <v>47.33</v>
       </c>
       <c r="G200">
-        <v>92.56</v>
+        <v>71.85</v>
       </c>
       <c r="H200">
-        <v>384.03</v>
+        <v>384.01</v>
       </c>
       <c r="I200">
-        <v>27</v>
+        <v>35.5</v>
       </c>
       <c r="J200">
-        <v>250</v>
+        <v>212.5</v>
       </c>
       <c r="K200">
         <v>1</v>
@@ -37988,10 +37988,10 @@
         <v>H-8 Cao độ chốt cáp so với yêu cầu thiết kế cọc</v>
       </c>
       <c r="V200">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="W200">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="X200" t="str">
         <v>CÓ</v>
@@ -41136,7 +41136,7 @@
         <v>Dây neo bờ dài nhất</v>
       </c>
       <c r="B244">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="C244" t="str">
         <v>m</v>
@@ -41147,7 +41147,7 @@
         <v>Số điểm có mặt đất tại cọc thấp hơn MNDB</v>
       </c>
       <c r="B245">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C245" t="str">
         <v>điểm</v>
@@ -41158,7 +41158,7 @@
         <v>Số điểm có đầu cọc ngập khi hồ ở MNLKT</v>
       </c>
       <c r="B246">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C246" t="str">
         <v>điểm</v>

--- a/docs/mat-bang-neo-9-be/bang_thong_ke_neo_9_be.xlsx
+++ b/docs/mat-bang-neo-9-be/bang_thong_ke_neo_9_be.xlsx
@@ -15014,13 +15014,13 @@
         <v>30.2</v>
       </c>
       <c r="R6">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="S6">
         <v>0.27</v>
       </c>
       <c r="T6">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="U6">
         <v>0</v>
@@ -15088,13 +15088,13 @@
         <v>30.2</v>
       </c>
       <c r="R7">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="S7">
         <v>0.27</v>
       </c>
       <c r="T7">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="U7">
         <v>0</v>
@@ -15162,16 +15162,16 @@
         <v>38.6</v>
       </c>
       <c r="R8">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="S8">
         <v>0.36</v>
       </c>
       <c r="T8">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="U8">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="V8">
         <v>0.15</v>
@@ -15236,16 +15236,16 @@
         <v>38.6</v>
       </c>
       <c r="R9">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="S9">
         <v>0.36</v>
       </c>
       <c r="T9">
-        <v>0.67</v>
+        <v>0.69</v>
       </c>
       <c r="U9">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="V9">
         <v>0.15</v>
@@ -15310,16 +15310,16 @@
         <v>38.6</v>
       </c>
       <c r="R10">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="S10">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="T10">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="U10">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="V10">
         <v>0.15</v>
@@ -15384,16 +15384,16 @@
         <v>73.7</v>
       </c>
       <c r="R11">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="S11">
         <v>0.55</v>
       </c>
       <c r="T11">
-        <v>0.92</v>
+        <v>0.94</v>
       </c>
       <c r="U11">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="V11">
         <v>0.15</v>
@@ -15458,16 +15458,16 @@
         <v>73.7</v>
       </c>
       <c r="R12">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="S12">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="T12">
-        <v>0.91</v>
+        <v>0.94</v>
       </c>
       <c r="U12">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="V12">
         <v>0.15</v>
@@ -15532,16 +15532,16 @@
         <v>73.7</v>
       </c>
       <c r="R13">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="S13">
         <v>0.67</v>
       </c>
       <c r="T13">
-        <v>0.94</v>
+        <v>0.97</v>
       </c>
       <c r="U13">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="V13">
         <v>0.15</v>
@@ -15582,19 +15582,19 @@
         <v>135.9</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K14">
         <v>0.4</v>
       </c>
       <c r="L14">
-        <v>3.58</v>
+        <v>4.21</v>
       </c>
       <c r="M14">
-        <v>165</v>
+        <v>202</v>
       </c>
       <c r="N14">
-        <v>9.2</v>
+        <v>10.8</v>
       </c>
       <c r="O14">
         <v>4</v>
@@ -15606,16 +15606,16 @@
         <v>73.7</v>
       </c>
       <c r="R14">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="S14">
-        <v>0.61</v>
+        <v>0.55</v>
       </c>
       <c r="T14">
-        <v>0.99</v>
+        <v>0.93</v>
       </c>
       <c r="U14">
-        <v>0.96</v>
+        <v>0.71</v>
       </c>
       <c r="V14">
         <v>0.15</v>
@@ -15680,16 +15680,16 @@
         <v>87.3</v>
       </c>
       <c r="R15">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="S15">
         <v>0.81</v>
       </c>
       <c r="T15">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="U15">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="V15">
         <v>0.15</v>
@@ -15754,16 +15754,16 @@
         <v>87.3</v>
       </c>
       <c r="R16">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="S16">
         <v>0.81</v>
       </c>
       <c r="T16">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="U16">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="V16">
         <v>0.15</v>
@@ -15828,16 +15828,16 @@
         <v>87.3</v>
       </c>
       <c r="R17">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="S17">
         <v>0.81</v>
       </c>
       <c r="T17">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="U17">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="V17">
         <v>0.15</v>
@@ -15902,16 +15902,16 @@
         <v>87.3</v>
       </c>
       <c r="R18">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="S18">
         <v>0.81</v>
       </c>
       <c r="T18">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="U18">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="V18">
         <v>0.15</v>
@@ -15976,16 +15976,16 @@
         <v>87.3</v>
       </c>
       <c r="R19">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="S19">
         <v>0.81</v>
       </c>
       <c r="T19">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="U19">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="V19">
         <v>0.15</v>
@@ -16050,16 +16050,16 @@
         <v>87.3</v>
       </c>
       <c r="R20">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="S20">
         <v>0.81</v>
       </c>
       <c r="T20">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="U20">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="V20">
         <v>0.15</v>
@@ -16124,16 +16124,16 @@
         <v>87.3</v>
       </c>
       <c r="R21">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="S21">
         <v>0.81</v>
       </c>
       <c r="T21">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="U21">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="V21">
         <v>0.15</v>
@@ -16198,16 +16198,16 @@
         <v>87.3</v>
       </c>
       <c r="R22">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="S22">
         <v>0.81</v>
       </c>
       <c r="T22">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="U22">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="V22">
         <v>0.15</v>
@@ -16272,16 +16272,16 @@
         <v>87.3</v>
       </c>
       <c r="R23">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="S23">
         <v>0.81</v>
       </c>
       <c r="T23">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="U23">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="V23">
         <v>0.15</v>
@@ -16346,16 +16346,16 @@
         <v>87.3</v>
       </c>
       <c r="R24">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="S24">
         <v>0.81</v>
       </c>
       <c r="T24">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="U24">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="V24">
         <v>0.15</v>
@@ -16420,16 +16420,16 @@
         <v>73.7</v>
       </c>
       <c r="R25">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="S25">
         <v>0.67</v>
       </c>
       <c r="T25">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="U25">
-        <v>0.75</v>
+        <v>0.81</v>
       </c>
       <c r="V25">
         <v>0.15</v>
@@ -16494,16 +16494,16 @@
         <v>73.7</v>
       </c>
       <c r="R26">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="S26">
         <v>0.67</v>
       </c>
       <c r="T26">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="U26">
-        <v>0.75</v>
+        <v>0.81</v>
       </c>
       <c r="V26">
         <v>0.15</v>
@@ -16568,16 +16568,16 @@
         <v>73.7</v>
       </c>
       <c r="R27">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="S27">
         <v>0.67</v>
       </c>
       <c r="T27">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="U27">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="V27">
         <v>0.15</v>
@@ -16642,16 +16642,16 @@
         <v>73.7</v>
       </c>
       <c r="R28">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="S28">
         <v>0.67</v>
       </c>
       <c r="T28">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="U28">
-        <v>0.75</v>
+        <v>0.81</v>
       </c>
       <c r="V28">
         <v>0.15</v>
@@ -16716,16 +16716,16 @@
         <v>73.7</v>
       </c>
       <c r="R29">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="S29">
         <v>0.67</v>
       </c>
       <c r="T29">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="U29">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="V29">
         <v>0.15</v>
@@ -16790,16 +16790,16 @@
         <v>87.3</v>
       </c>
       <c r="R30">
-        <v>0.56</v>
+        <v>0.59</v>
       </c>
       <c r="S30">
         <v>0.81</v>
       </c>
       <c r="T30">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="U30">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="V30">
         <v>0.15</v>
@@ -16864,16 +16864,16 @@
         <v>87.3</v>
       </c>
       <c r="R31">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="S31">
-        <v>0.81</v>
+        <v>0.85</v>
       </c>
       <c r="T31">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="U31">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="V31">
         <v>0.15</v>
@@ -16938,16 +16938,16 @@
         <v>87.3</v>
       </c>
       <c r="R32">
-        <v>0.56</v>
+        <v>0.58</v>
       </c>
       <c r="S32">
         <v>0.81</v>
       </c>
       <c r="T32">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="U32">
-        <v>0.65</v>
+        <v>0.69</v>
       </c>
       <c r="V32">
         <v>0.15</v>
@@ -17012,16 +17012,16 @@
         <v>59.1</v>
       </c>
       <c r="R33">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="S33">
         <v>0.59</v>
       </c>
       <c r="T33">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="U33">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="V33">
         <v>0.15</v>
@@ -17086,16 +17086,16 @@
         <v>59.1</v>
       </c>
       <c r="R34">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="S34">
         <v>0.59</v>
       </c>
       <c r="T34">
-        <v>0.79</v>
+        <v>0.81</v>
       </c>
       <c r="U34">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="V34">
         <v>0.15</v>
@@ -17160,16 +17160,16 @@
         <v>59.1</v>
       </c>
       <c r="R35">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="S35">
         <v>0.59</v>
       </c>
       <c r="T35">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="U35">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="V35">
         <v>0.15</v>
@@ -17234,16 +17234,16 @@
         <v>59.1</v>
       </c>
       <c r="R36">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="S36">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="T36">
-        <v>0.91</v>
+        <v>0.94</v>
       </c>
       <c r="U36">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="V36">
         <v>0.15</v>
@@ -17308,16 +17308,16 @@
         <v>59.1</v>
       </c>
       <c r="R37">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="S37">
         <v>0.59</v>
       </c>
       <c r="T37">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="U37">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="V37">
         <v>0.15</v>
@@ -17377,7 +17377,7 @@
         <v>Tổng bê tông đế</v>
       </c>
       <c r="B43">
-        <v>92.2</v>
+        <v>92.8</v>
       </c>
       <c r="C43" t="str">
         <v>m³</v>
@@ -17388,7 +17388,7 @@
         <v>Tổng thép bản đế (ước tính)</v>
       </c>
       <c r="B44">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="C44" t="str">
         <v>tấn</v>
@@ -17562,25 +17562,25 @@
         <v>Ø12 a200</v>
       </c>
       <c r="F4">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="G4">
-        <v>29.7</v>
+        <v>31</v>
       </c>
       <c r="H4">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="I4">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="J4">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="K4">
         <v>0.33</v>
       </c>
       <c r="L4">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -17615,25 +17615,25 @@
         <v>Ø12 a200</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>8.2</v>
       </c>
       <c r="G5">
-        <v>36.5</v>
+        <v>37.9</v>
       </c>
       <c r="H5">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="I5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="J5">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="K5">
         <v>0.3</v>
       </c>
       <c r="L5">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -17668,28 +17668,28 @@
         <v>Ø12 a200</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>8.2</v>
       </c>
       <c r="G6">
-        <v>36.5</v>
+        <v>37.9</v>
       </c>
       <c r="H6">
-        <v>38.4</v>
+        <v>38.2</v>
       </c>
       <c r="I6">
-        <v>23</v>
+        <v>23.7</v>
       </c>
       <c r="J6">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="K6">
         <v>0.42</v>
       </c>
       <c r="L6">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="M6">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="N6">
         <v>0.15</v>
@@ -17721,28 +17721,28 @@
         <v>Ø12 a200</v>
       </c>
       <c r="F7">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>35.6</v>
+        <v>37</v>
       </c>
       <c r="H7">
-        <v>73.3</v>
+        <v>73</v>
       </c>
       <c r="I7">
-        <v>42.8</v>
+        <v>44.3</v>
       </c>
       <c r="J7">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="K7">
         <v>0.72</v>
       </c>
       <c r="L7">
-        <v>0.92</v>
+        <v>0.94</v>
       </c>
       <c r="M7">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="N7">
         <v>0.15</v>
@@ -17774,28 +17774,28 @@
         <v>Ø12 a200</v>
       </c>
       <c r="F8">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="G8">
-        <v>19.1</v>
+        <v>20</v>
       </c>
       <c r="H8">
-        <v>87.2</v>
+        <v>87.1</v>
       </c>
       <c r="I8">
-        <v>28.6</v>
+        <v>29.9</v>
       </c>
       <c r="J8">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="K8">
         <v>0.86</v>
       </c>
       <c r="L8">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="M8">
-        <v>0.69</v>
+        <v>0.73</v>
       </c>
       <c r="N8">
         <v>0.15</v>
@@ -17827,28 +17827,28 @@
         <v>Ø12 a200</v>
       </c>
       <c r="F9">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="G9">
-        <v>30.5</v>
+        <v>31.8</v>
       </c>
       <c r="H9">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="I9">
-        <v>23.1</v>
+        <v>24</v>
       </c>
       <c r="J9">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="K9">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="L9">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="M9">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="N9">
         <v>0.15</v>
@@ -17880,25 +17880,25 @@
         <v>Ø12 a200</v>
       </c>
       <c r="F10">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="G10">
-        <v>19.1</v>
+        <v>20</v>
       </c>
       <c r="H10">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="I10">
-        <v>13.4</v>
+        <v>14</v>
       </c>
       <c r="J10">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="K10">
         <v>0.44</v>
       </c>
       <c r="L10">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -17933,28 +17933,28 @@
         <v>Ø12 a200</v>
       </c>
       <c r="F11">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="G11">
-        <v>30.5</v>
+        <v>31.8</v>
       </c>
       <c r="H11">
-        <v>58.9</v>
+        <v>58.7</v>
       </c>
       <c r="I11">
-        <v>30</v>
+        <v>31.1</v>
       </c>
       <c r="J11">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="K11">
         <v>0.64</v>
       </c>
       <c r="L11">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="M11">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="N11">
         <v>0.15</v>
@@ -17986,22 +17986,22 @@
         <v>Ø12 a200</v>
       </c>
       <c r="F12">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="G12">
-        <v>30.3</v>
+        <v>31.6</v>
       </c>
       <c r="H12">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="I12">
-        <v>15.6</v>
+        <v>16.2</v>
       </c>
       <c r="J12">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="K12">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="L12">
         <v>0.41</v>
@@ -18031,7 +18031,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI51"/>
+  <dimension ref="A1:AI50"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
@@ -18258,10 +18258,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S7">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T7">
-        <v>28.7</v>
+        <v>29.7</v>
       </c>
       <c r="U7">
         <v>2.5</v>
@@ -18282,13 +18282,13 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA7">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="AB7">
         <v>0.27</v>
       </c>
       <c r="AC7">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -18368,7 +18368,7 @@
         <v>2.1</v>
       </c>
       <c r="T8">
-        <v>31</v>
+        <v>32.1</v>
       </c>
       <c r="U8">
         <v>2.5</v>
@@ -18389,13 +18389,13 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA8">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="AB8">
         <v>0.27</v>
       </c>
       <c r="AC8">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -18472,10 +18472,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S9">
-        <v>8.9</v>
+        <v>8.7</v>
       </c>
       <c r="T9">
-        <v>38.4</v>
+        <v>39.7</v>
       </c>
       <c r="U9">
         <v>2.5</v>
@@ -18496,16 +18496,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA9">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="AB9">
         <v>0.36</v>
       </c>
       <c r="AC9">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="AD9">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="AE9">
         <v>0.15</v>
@@ -18514,7 +18514,7 @@
         <v>0.62</v>
       </c>
       <c r="AG9">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="AH9" t="str">
         <v>ĐẠT</v>
@@ -18579,10 +18579,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S10">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="T10">
-        <v>41.3</v>
+        <v>42.5</v>
       </c>
       <c r="U10">
         <v>2.5</v>
@@ -18603,16 +18603,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA10">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="AB10">
         <v>0.36</v>
       </c>
       <c r="AC10">
-        <v>0.67</v>
+        <v>0.69</v>
       </c>
       <c r="AD10">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="AE10">
         <v>0.15</v>
@@ -18621,7 +18621,7 @@
         <v>0.62</v>
       </c>
       <c r="AG10">
-        <v>0.67</v>
+        <v>0.69</v>
       </c>
       <c r="AH10" t="str">
         <v>ĐẠT</v>
@@ -18686,10 +18686,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S11">
-        <v>9.7</v>
+        <v>9.6</v>
       </c>
       <c r="T11">
-        <v>29.8</v>
+        <v>31</v>
       </c>
       <c r="U11">
         <v>2.5</v>
@@ -18710,16 +18710,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA11">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="AB11">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AC11">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="AD11">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="AE11">
         <v>0.15</v>
@@ -18793,10 +18793,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S12">
-        <v>27.8</v>
+        <v>27.3</v>
       </c>
       <c r="T12">
-        <v>68.2</v>
+        <v>70.3</v>
       </c>
       <c r="U12">
         <v>3.25</v>
@@ -18817,16 +18817,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA12">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AB12">
         <v>0.55</v>
       </c>
       <c r="AC12">
-        <v>0.92</v>
+        <v>0.94</v>
       </c>
       <c r="AD12">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="AE12">
         <v>0.15</v>
@@ -18835,7 +18835,7 @@
         <v>0.62</v>
       </c>
       <c r="AG12">
-        <v>0.92</v>
+        <v>0.94</v>
       </c>
       <c r="AH12" t="str">
         <v>ĐẠT</v>
@@ -18900,10 +18900,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S13">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="T13">
-        <v>47.5</v>
+        <v>49.4</v>
       </c>
       <c r="U13">
         <v>2.5</v>
@@ -18924,16 +18924,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA13">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AB13">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="AC13">
-        <v>0.91</v>
+        <v>0.94</v>
       </c>
       <c r="AD13">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="AE13">
         <v>0.15</v>
@@ -18942,7 +18942,7 @@
         <v>0.62</v>
       </c>
       <c r="AG13">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="AH13" t="str">
         <v>ĐẠT</v>
@@ -19007,10 +19007,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S14">
-        <v>30.3</v>
+        <v>29.9</v>
       </c>
       <c r="T14">
-        <v>56.3</v>
+        <v>58.3</v>
       </c>
       <c r="U14">
         <v>2.75</v>
@@ -19031,16 +19031,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA14">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="AB14">
         <v>0.67</v>
       </c>
       <c r="AC14">
-        <v>0.94</v>
+        <v>0.97</v>
       </c>
       <c r="AD14">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AE14">
         <v>0.15</v>
@@ -19049,7 +19049,7 @@
         <v>0.62</v>
       </c>
       <c r="AG14">
-        <v>0.94</v>
+        <v>0.98</v>
       </c>
       <c r="AH14" t="str">
         <v>ĐẠT</v>
@@ -19114,40 +19114,40 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S15">
-        <v>28.1</v>
+        <v>27.6</v>
       </c>
       <c r="T15">
-        <v>67.1</v>
+        <v>69.2</v>
       </c>
       <c r="U15">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V15">
         <v>0.4</v>
       </c>
       <c r="W15">
-        <v>54</v>
+        <v>63.4</v>
       </c>
       <c r="X15">
-        <v>3.58</v>
+        <v>4.21</v>
       </c>
       <c r="Y15">
-        <v>9.2</v>
+        <v>10.8</v>
       </c>
       <c r="Z15" t="str">
         <v>Ø12 a200</v>
       </c>
       <c r="AA15">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="AB15">
-        <v>0.61</v>
+        <v>0.55</v>
       </c>
       <c r="AC15">
-        <v>0.99</v>
+        <v>0.93</v>
       </c>
       <c r="AD15">
-        <v>0.96</v>
+        <v>0.71</v>
       </c>
       <c r="AE15">
         <v>0.15</v>
@@ -19156,7 +19156,7 @@
         <v>0.62</v>
       </c>
       <c r="AG15">
-        <v>0.99</v>
+        <v>0.93</v>
       </c>
       <c r="AH15" t="str">
         <v>ĐẠT</v>
@@ -19221,10 +19221,10 @@
         <v>B5A-D32 căng, B3A-D36 chùng (MN cao)</v>
       </c>
       <c r="S16">
-        <v>77.9</v>
+        <v>77.5</v>
       </c>
       <c r="T16">
-        <v>29.9</v>
+        <v>31.2</v>
       </c>
       <c r="U16">
         <v>2.75</v>
@@ -19245,16 +19245,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA16">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="AB16">
         <v>0.81</v>
       </c>
       <c r="AC16">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AD16">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AE16">
         <v>0.15</v>
@@ -19263,7 +19263,7 @@
         <v>0.62</v>
       </c>
       <c r="AG16">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AH16" t="str">
         <v>ĐẠT</v>
@@ -19328,10 +19328,10 @@
         <v>B5A-D31 căng, B3A-D37 chùng (MN cao)</v>
       </c>
       <c r="S17">
-        <v>77.9</v>
+        <v>77.5</v>
       </c>
       <c r="T17">
-        <v>29.9</v>
+        <v>31.2</v>
       </c>
       <c r="U17">
         <v>2.75</v>
@@ -19352,16 +19352,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA17">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="AB17">
         <v>0.81</v>
       </c>
       <c r="AC17">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AD17">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AE17">
         <v>0.15</v>
@@ -19370,7 +19370,7 @@
         <v>0.62</v>
       </c>
       <c r="AG17">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AH17" t="str">
         <v>ĐẠT</v>
@@ -19435,10 +19435,10 @@
         <v>B5A-D30 căng, B3A-D38 chùng (MN cao)</v>
       </c>
       <c r="S18">
-        <v>77.9</v>
+        <v>77.5</v>
       </c>
       <c r="T18">
-        <v>30</v>
+        <v>31.3</v>
       </c>
       <c r="U18">
         <v>2.75</v>
@@ -19459,16 +19459,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA18">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="AB18">
         <v>0.81</v>
       </c>
       <c r="AC18">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AD18">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="AE18">
         <v>0.15</v>
@@ -19477,7 +19477,7 @@
         <v>0.62</v>
       </c>
       <c r="AG18">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AH18" t="str">
         <v>ĐẠT</v>
@@ -19542,10 +19542,10 @@
         <v>B5A-D29 căng, B3A-D39 chùng (MN cao)</v>
       </c>
       <c r="S19">
-        <v>77.9</v>
+        <v>77.5</v>
       </c>
       <c r="T19">
-        <v>30</v>
+        <v>31.3</v>
       </c>
       <c r="U19">
         <v>2.75</v>
@@ -19566,16 +19566,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA19">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="AB19">
         <v>0.81</v>
       </c>
       <c r="AC19">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AD19">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="AE19">
         <v>0.15</v>
@@ -19584,7 +19584,7 @@
         <v>0.62</v>
       </c>
       <c r="AG19">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AH19" t="str">
         <v>ĐẠT</v>
@@ -19649,10 +19649,10 @@
         <v>B5A-D28 căng, B3A-D40 chùng (MN cao)</v>
       </c>
       <c r="S20">
-        <v>77.9</v>
+        <v>77.5</v>
       </c>
       <c r="T20">
-        <v>29.9</v>
+        <v>31.2</v>
       </c>
       <c r="U20">
         <v>2.75</v>
@@ -19673,16 +19673,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA20">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="AB20">
         <v>0.81</v>
       </c>
       <c r="AC20">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AD20">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AE20">
         <v>0.15</v>
@@ -19691,7 +19691,7 @@
         <v>0.62</v>
       </c>
       <c r="AG20">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AH20" t="str">
         <v>ĐẠT</v>
@@ -19756,10 +19756,10 @@
         <v>B5A-D27 căng, B3A-D41 chùng (MN cao)</v>
       </c>
       <c r="S21">
-        <v>77.9</v>
+        <v>77.5</v>
       </c>
       <c r="T21">
-        <v>29.9</v>
+        <v>31.2</v>
       </c>
       <c r="U21">
         <v>2.75</v>
@@ -19780,16 +19780,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA21">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="AB21">
         <v>0.81</v>
       </c>
       <c r="AC21">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AD21">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AE21">
         <v>0.15</v>
@@ -19798,7 +19798,7 @@
         <v>0.62</v>
       </c>
       <c r="AG21">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AH21" t="str">
         <v>ĐẠT</v>
@@ -19863,10 +19863,10 @@
         <v>B5A-D26 căng, B3A-D42 chùng (MN cao)</v>
       </c>
       <c r="S22">
-        <v>77.9</v>
+        <v>77.5</v>
       </c>
       <c r="T22">
-        <v>29.8</v>
+        <v>31.1</v>
       </c>
       <c r="U22">
         <v>2.75</v>
@@ -19887,16 +19887,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA22">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="AB22">
         <v>0.81</v>
       </c>
       <c r="AC22">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AD22">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AE22">
         <v>0.15</v>
@@ -19905,7 +19905,7 @@
         <v>0.62</v>
       </c>
       <c r="AG22">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AH22" t="str">
         <v>ĐẠT</v>
@@ -19970,10 +19970,10 @@
         <v>B5A-D25 căng, B3A-D43 chùng (MN cao)</v>
       </c>
       <c r="S23">
-        <v>77.9</v>
+        <v>77.5</v>
       </c>
       <c r="T23">
-        <v>29.8</v>
+        <v>31.1</v>
       </c>
       <c r="U23">
         <v>2.75</v>
@@ -19994,16 +19994,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA23">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="AB23">
         <v>0.81</v>
       </c>
       <c r="AC23">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AD23">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AE23">
         <v>0.15</v>
@@ -20012,7 +20012,7 @@
         <v>0.62</v>
       </c>
       <c r="AG23">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AH23" t="str">
         <v>ĐẠT</v>
@@ -20077,10 +20077,10 @@
         <v>B5A-D24 căng, B3A-D44 chùng (MN cao)</v>
       </c>
       <c r="S24">
-        <v>77.9</v>
+        <v>77.5</v>
       </c>
       <c r="T24">
-        <v>29.8</v>
+        <v>31.1</v>
       </c>
       <c r="U24">
         <v>2.75</v>
@@ -20101,16 +20101,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA24">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="AB24">
         <v>0.81</v>
       </c>
       <c r="AC24">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AD24">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AE24">
         <v>0.15</v>
@@ -20119,7 +20119,7 @@
         <v>0.62</v>
       </c>
       <c r="AG24">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AH24" t="str">
         <v>ĐẠT</v>
@@ -20184,10 +20184,10 @@
         <v>B5A-D23 căng, B3A-D45 chùng (MN cao)</v>
       </c>
       <c r="S25">
-        <v>77.9</v>
+        <v>77.5</v>
       </c>
       <c r="T25">
-        <v>29.8</v>
+        <v>31.1</v>
       </c>
       <c r="U25">
         <v>2.75</v>
@@ -20208,16 +20208,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA25">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="AB25">
         <v>0.81</v>
       </c>
       <c r="AC25">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AD25">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AE25">
         <v>0.15</v>
@@ -20226,7 +20226,7 @@
         <v>0.62</v>
       </c>
       <c r="AG25">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AH25" t="str">
         <v>ĐẠT</v>
@@ -20291,10 +20291,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S26">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="T26">
-        <v>53.2</v>
+        <v>55.3</v>
       </c>
       <c r="U26">
         <v>2.75</v>
@@ -20315,16 +20315,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA26">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="AB26">
         <v>0.67</v>
       </c>
       <c r="AC26">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AD26">
-        <v>0.75</v>
+        <v>0.81</v>
       </c>
       <c r="AE26">
         <v>0.15</v>
@@ -20333,7 +20333,7 @@
         <v>0.62</v>
       </c>
       <c r="AG26">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AH26" t="str">
         <v>ĐẠT</v>
@@ -20398,10 +20398,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S27">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="T27">
-        <v>53.1</v>
+        <v>55.2</v>
       </c>
       <c r="U27">
         <v>2.75</v>
@@ -20422,16 +20422,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA27">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="AB27">
         <v>0.67</v>
       </c>
       <c r="AC27">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AD27">
-        <v>0.75</v>
+        <v>0.81</v>
       </c>
       <c r="AE27">
         <v>0.15</v>
@@ -20440,7 +20440,7 @@
         <v>0.62</v>
       </c>
       <c r="AG27">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AH27" t="str">
         <v>ĐẠT</v>
@@ -20505,10 +20505,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S28">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="T28">
-        <v>53.3</v>
+        <v>55.3</v>
       </c>
       <c r="U28">
         <v>2.75</v>
@@ -20529,16 +20529,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA28">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="AB28">
         <v>0.67</v>
       </c>
       <c r="AC28">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AD28">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="AE28">
         <v>0.15</v>
@@ -20547,7 +20547,7 @@
         <v>0.62</v>
       </c>
       <c r="AG28">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AH28" t="str">
         <v>ĐẠT</v>
@@ -20612,10 +20612,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S29">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="T29">
-        <v>53.2</v>
+        <v>55.3</v>
       </c>
       <c r="U29">
         <v>2.75</v>
@@ -20636,16 +20636,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA29">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="AB29">
         <v>0.67</v>
       </c>
       <c r="AC29">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AD29">
-        <v>0.75</v>
+        <v>0.81</v>
       </c>
       <c r="AE29">
         <v>0.15</v>
@@ -20654,7 +20654,7 @@
         <v>0.62</v>
       </c>
       <c r="AG29">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AH29" t="str">
         <v>ĐẠT</v>
@@ -20719,10 +20719,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S30">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="T30">
-        <v>53.3</v>
+        <v>55.4</v>
       </c>
       <c r="U30">
         <v>2.75</v>
@@ -20743,16 +20743,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA30">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="AB30">
         <v>0.67</v>
       </c>
       <c r="AC30">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AD30">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="AE30">
         <v>0.15</v>
@@ -20761,7 +20761,7 @@
         <v>0.62</v>
       </c>
       <c r="AG30">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="AH30" t="str">
         <v>ĐẠT</v>
@@ -20826,10 +20826,10 @@
         <v>B5A-D13 căng, B6-D27 chùng (MN cao)</v>
       </c>
       <c r="S31">
-        <v>78.1</v>
+        <v>77.7</v>
       </c>
       <c r="T31">
-        <v>29.4</v>
+        <v>30.7</v>
       </c>
       <c r="U31">
         <v>2.75</v>
@@ -20850,16 +20850,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA31">
-        <v>0.56</v>
+        <v>0.59</v>
       </c>
       <c r="AB31">
         <v>0.81</v>
       </c>
       <c r="AC31">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="AD31">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="AE31">
         <v>0.15</v>
@@ -20868,7 +20868,7 @@
         <v>0.62</v>
       </c>
       <c r="AG31">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="AH31" t="str">
         <v>ĐẠT</v>
@@ -20933,10 +20933,10 @@
         <v>B5A-D14 căng, B6-D31 chùng (MN cao)</v>
       </c>
       <c r="S32">
-        <v>77.2</v>
+        <v>76.7</v>
       </c>
       <c r="T32">
-        <v>32.1</v>
+        <v>33.5</v>
       </c>
       <c r="U32">
         <v>2.75</v>
@@ -20957,16 +20957,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA32">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="AB32">
-        <v>0.81</v>
+        <v>0.85</v>
       </c>
       <c r="AC32">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="AD32">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="AE32">
         <v>0.15</v>
@@ -20975,7 +20975,7 @@
         <v>0.62</v>
       </c>
       <c r="AG32">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="AH32" t="str">
         <v>ĐẠT</v>
@@ -21040,10 +21040,10 @@
         <v>B5A-D15 căng, B6-D17 chùng (MN cao)</v>
       </c>
       <c r="S33">
-        <v>78.1</v>
+        <v>77.7</v>
       </c>
       <c r="T33">
-        <v>29.2</v>
+        <v>30.5</v>
       </c>
       <c r="U33">
         <v>2.75</v>
@@ -21064,16 +21064,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA33">
-        <v>0.56</v>
+        <v>0.58</v>
       </c>
       <c r="AB33">
         <v>0.81</v>
       </c>
       <c r="AC33">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AD33">
-        <v>0.65</v>
+        <v>0.69</v>
       </c>
       <c r="AE33">
         <v>0.15</v>
@@ -21082,7 +21082,7 @@
         <v>0.62</v>
       </c>
       <c r="AG33">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="AH33" t="str">
         <v>ĐẠT</v>
@@ -21147,10 +21147,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S34">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="T34">
-        <v>55.2</v>
+        <v>57.1</v>
       </c>
       <c r="U34">
         <v>2.5</v>
@@ -21171,16 +21171,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA34">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="AB34">
         <v>0.59</v>
       </c>
       <c r="AC34">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="AD34">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="AE34">
         <v>0.15</v>
@@ -21189,7 +21189,7 @@
         <v>0.62</v>
       </c>
       <c r="AG34">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="AH34" t="str">
         <v>ĐẠT</v>
@@ -21254,10 +21254,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S35">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="T35">
-        <v>47.7</v>
+        <v>49.5</v>
       </c>
       <c r="U35">
         <v>2.5</v>
@@ -21278,16 +21278,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA35">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="AB35">
         <v>0.59</v>
       </c>
       <c r="AC35">
-        <v>0.79</v>
+        <v>0.81</v>
       </c>
       <c r="AD35">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="AE35">
         <v>0.15</v>
@@ -21296,7 +21296,7 @@
         <v>0.62</v>
       </c>
       <c r="AG35">
-        <v>0.79</v>
+        <v>0.81</v>
       </c>
       <c r="AH35" t="str">
         <v>ĐẠT</v>
@@ -21361,10 +21361,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S36">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="T36">
-        <v>54.4</v>
+        <v>56.3</v>
       </c>
       <c r="U36">
         <v>2.5</v>
@@ -21385,16 +21385,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA36">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AB36">
         <v>0.59</v>
       </c>
       <c r="AC36">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="AD36">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="AE36">
         <v>0.15</v>
@@ -21403,7 +21403,7 @@
         <v>0.62</v>
       </c>
       <c r="AG36">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="AH36" t="str">
         <v>ĐẠT</v>
@@ -21468,10 +21468,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S37">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="T37">
-        <v>56</v>
+        <v>57.9</v>
       </c>
       <c r="U37">
         <v>2.5</v>
@@ -21492,16 +21492,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA37">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="AB37">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="AC37">
-        <v>0.91</v>
+        <v>0.94</v>
       </c>
       <c r="AD37">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AE37">
         <v>0.15</v>
@@ -21510,7 +21510,7 @@
         <v>0.62</v>
       </c>
       <c r="AG37">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AH37" t="str">
         <v>ĐẠT</v>
@@ -21575,10 +21575,10 @@
         <v>cả hai dây căng (MN cao)</v>
       </c>
       <c r="S38">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="T38">
-        <v>47.6</v>
+        <v>49.2</v>
       </c>
       <c r="U38">
         <v>2.5</v>
@@ -21599,16 +21599,16 @@
         <v>Ø12 a200</v>
       </c>
       <c r="AA38">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AB38">
         <v>0.59</v>
       </c>
       <c r="AC38">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="AD38">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="AE38">
         <v>0.15</v>
@@ -21617,7 +21617,7 @@
         <v>0.62</v>
       </c>
       <c r="AG38">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="AH38" t="str">
         <v>ĐẠT</v>
@@ -21685,7 +21685,7 @@
         <v>Bê tông đế</v>
       </c>
       <c r="B45">
-        <v>92.2</v>
+        <v>92.8</v>
       </c>
       <c r="C45" t="str">
         <v>m³</v>
@@ -21726,10 +21726,10 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Số đế cạnh B = 3,00 m</v>
+        <v>Số đế cạnh B = 3,25 m</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49" t="str">
         <v>đế</v>
@@ -21737,29 +21737,18 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Số đế cạnh B = 3,25 m</v>
+        <v>Số đế mà địa hình IFC cao hơn đáy thiết kế trên 0,5 m (cần kiểm tra khảo sát / nạo vét)</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C50" t="str">
         <v>đế</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>Số đế mà địa hình IFC cao hơn đáy thiết kế trên 0,5 m (cần kiểm tra khảo sát / nạo vét)</v>
-      </c>
-      <c r="B51">
-        <v>4</v>
-      </c>
-      <c r="C51" t="str">
-        <v>đế</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AI51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AI50"/>
   </ignoredErrors>
 </worksheet>
 </file>
